--- a/TEAM.xlsx
+++ b/TEAM.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <workbookPr showObjects="none" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DA220A-AA3D-45E2-B0C4-AEE026A0551E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EB6EE5-9091-4B5F-AF65-C9A828263573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{3AF6BCC7-0372-4EF8-A651-596D3CC14EF5}"/>
+    <workbookView xWindow="14235" yWindow="90" windowWidth="33210" windowHeight="20805" activeTab="1" xr2:uid="{3AF6BCC7-0372-4EF8-A651-596D3CC14EF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Model" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,8 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={404C3A6C-57D9-462B-8169-03AF44C46401}</author>
-    <author>tc={81C416ED-B805-4A5E-90CB-C684086667DC}</author>
+    <author>tc={B0D31656-8A16-4E18-8B61-E7D1D442A65E}</author>
+    <author>tc={18DD1B87-6DD2-44AB-8575-BA937C652995}</author>
   </authors>
   <commentList>
     <comment ref="K15" authorId="0" shapeId="0" xr:uid="{404C3A6C-57D9-462B-8169-03AF44C46401}">
@@ -50,12 +54,20 @@
     FQ22 guidance: 690-705</t>
       </text>
     </comment>
-    <comment ref="L15" authorId="1" shapeId="0" xr:uid="{81C416ED-B805-4A5E-90CB-C684086667DC}">
+    <comment ref="L15" authorId="1" shapeId="0" xr:uid="{B0D31656-8A16-4E18-8B61-E7D1D442A65E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    FQ322 guidance: 710-725</t>
+    FQ22 guidance: 690-705</t>
+      </text>
+    </comment>
+    <comment ref="M15" authorId="2" shapeId="0" xr:uid="{18DD1B87-6DD2-44AB-8575-BA937C652995}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    FQ22 guidance: 690-705</t>
       </text>
     </comment>
   </commentList>
@@ -63,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="84">
   <si>
     <t>Price</t>
   </si>
@@ -210,16 +222,127 @@
   </si>
   <si>
     <t>FQ223</t>
+  </si>
+  <si>
+    <t>FQ323</t>
+  </si>
+  <si>
+    <t>FQ423</t>
+  </si>
+  <si>
+    <t>FQ124</t>
+  </si>
+  <si>
+    <t>FQ224</t>
+  </si>
+  <si>
+    <t>FQ324</t>
+  </si>
+  <si>
+    <t>FY21</t>
+  </si>
+  <si>
+    <t>FY22</t>
+  </si>
+  <si>
+    <t>FY23</t>
+  </si>
+  <si>
+    <t>FY24</t>
+  </si>
+  <si>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>FY26</t>
+  </si>
+  <si>
+    <t>FY27</t>
+  </si>
+  <si>
+    <t>FY28</t>
+  </si>
+  <si>
+    <t>FY29</t>
+  </si>
+  <si>
+    <t>FY30</t>
+  </si>
+  <si>
+    <t>FY31</t>
+  </si>
+  <si>
+    <t>FY32</t>
+  </si>
+  <si>
+    <t>FY33</t>
+  </si>
+  <si>
+    <t>FY34</t>
+  </si>
+  <si>
+    <t>FY35</t>
+  </si>
+  <si>
+    <t>FY36</t>
+  </si>
+  <si>
+    <t>FY37</t>
+  </si>
+  <si>
+    <t>FY38</t>
+  </si>
+  <si>
+    <t>FY39</t>
+  </si>
+  <si>
+    <t>FY40</t>
+  </si>
+  <si>
+    <t>FY41</t>
+  </si>
+  <si>
+    <t>FQ424</t>
+  </si>
+  <si>
+    <t>Rev Growth</t>
+  </si>
+  <si>
+    <t>Growth Rate</t>
+  </si>
+  <si>
+    <t>Terminal Rate</t>
+  </si>
+  <si>
+    <t>Discount Rate</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Share Price</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>Market Cap</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
+  <numFmts count="7">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="171" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -240,16 +363,39 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -257,12 +403,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -289,13 +453,36 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="5">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -367,6 +554,30 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="L2">
+            <v>722</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Martin Shkreli" id="{691673F2-D878-4E73-9BD7-049390760563}" userId="9ffda80931a57275" providerId="Windows Live"/>
@@ -374,9 +585,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -414,7 +625,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -520,7 +731,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -662,7 +873,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -673,8 +884,11 @@
   <threadedComment ref="K15" dT="2022-07-27T14:40:47.90" personId="{691673F2-D878-4E73-9BD7-049390760563}" id="{404C3A6C-57D9-462B-8169-03AF44C46401}">
     <text>FQ22 guidance: 690-705</text>
   </threadedComment>
-  <threadedComment ref="L15" dT="2022-07-27T14:37:17.16" personId="{691673F2-D878-4E73-9BD7-049390760563}" id="{81C416ED-B805-4A5E-90CB-C684086667DC}">
-    <text>FQ322 guidance: 710-725</text>
+  <threadedComment ref="L15" dT="2022-07-27T14:40:47.90" personId="{691673F2-D878-4E73-9BD7-049390760563}" id="{B0D31656-8A16-4E18-8B61-E7D1D442A65E}">
+    <text>FQ22 guidance: 690-705</text>
+  </threadedComment>
+  <threadedComment ref="M15" dT="2022-07-27T14:40:47.90" personId="{691673F2-D878-4E73-9BD7-049390760563}" id="{18DD1B87-6DD2-44AB-8575-BA937C652995}">
+    <text>FQ22 guidance: 690-705</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -692,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>190.85</v>
+        <v>179.45</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
@@ -703,7 +917,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>253.72300000000001</v>
+        <v>259.71699999999998</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>6</v>
@@ -718,7 +932,7 @@
       </c>
       <c r="L4" s="1">
         <f>+L2*L3</f>
-        <v>48423.034550000004</v>
+        <v>46606.215649999991</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
@@ -753,7 +967,7 @@
       </c>
       <c r="L7" s="1">
         <f>+L4-L5+L6</f>
-        <v>47990.635550000006</v>
+        <v>46173.816649999993</v>
       </c>
     </row>
   </sheetData>
@@ -763,7 +977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF29F7FA-B9F0-42C1-B494-BA78776DB519}">
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:AQ37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -773,9 +987,14 @@
     <col min="7" max="9" width="9.140625" style="2"/>
     <col min="10" max="10" width="10.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="9.140625" style="2"/>
+    <col min="19" max="19" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" style="16"/>
+    <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" customWidth="1"/>
+    <col min="28" max="28" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>7</v>
       </c>
@@ -824,8 +1043,11 @@
       <c r="R1" s="12">
         <v>45291</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S1" s="13">
+        <v>45382</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C2" s="2" t="s">
         <v>39</v>
       </c>
@@ -862,8 +1084,89 @@
       <c r="N2" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="W2" t="s">
+        <v>54</v>
+      </c>
+      <c r="X2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>46</v>
       </c>
@@ -897,8 +1200,20 @@
       <c r="N3" s="3">
         <v>253177</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O3" s="3">
+        <v>259775</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>265000</v>
+      </c>
+      <c r="R3" s="1">
+        <v>302000</v>
+      </c>
+      <c r="S3" s="1">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
@@ -923,13 +1238,38 @@
       <c r="K7" s="3">
         <v>399.45299999999997</v>
       </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="L7" s="3">
+        <f>1515.424-SUM(I7:K7)</f>
+        <v>433.96900000000005</v>
+      </c>
+      <c r="M7" s="1">
+        <v>475.04300000000001</v>
+      </c>
       <c r="N7" s="3">
         <v>512.33500000000004</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O7" s="1">
+        <v>534.89099999999996</v>
+      </c>
+      <c r="P7" s="1">
+        <f>2085.498-SUM(M7:O7)</f>
+        <v>563.22900000000004</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>604.64700000000005</v>
+      </c>
+      <c r="R7" s="1">
+        <v>653.21</v>
+      </c>
+      <c r="S7" s="1">
+        <v>703.03599999999994</v>
+      </c>
+      <c r="T7" s="18">
+        <f>P7*1.32</f>
+        <v>743.46228000000008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>28</v>
       </c>
@@ -954,13 +1294,38 @@
       <c r="K8" s="3">
         <v>151.095</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="L8" s="3">
+        <f>560.319-SUM(I8:K8)</f>
+        <v>158.92099999999994</v>
+      </c>
+      <c r="M8" s="3">
+        <v>161.22800000000001</v>
+      </c>
       <c r="N8" s="3">
         <v>194.26400000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O8" s="1">
+        <v>221.55099999999999</v>
+      </c>
+      <c r="P8" s="1">
+        <f>819.251-SUM(M8:O8)</f>
+        <v>242.20799999999997</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>242.94300000000001</v>
+      </c>
+      <c r="R8" s="1">
+        <v>274.75799999999998</v>
+      </c>
+      <c r="S8" s="1">
+        <v>364.13400000000001</v>
+      </c>
+      <c r="T8" s="18">
+        <f>P8*1.41</f>
+        <v>341.51327999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>29</v>
       </c>
@@ -985,13 +1350,37 @@
       <c r="K9" s="3">
         <v>132.333</v>
       </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="L9" s="3">
+        <f>525.028-SUM(I9:K9)</f>
+        <v>117.62900000000002</v>
+      </c>
+      <c r="M9" s="3">
+        <v>113.813</v>
+      </c>
       <c r="N9" s="3">
         <v>106.16800000000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O9" s="1">
+        <v>94.388999999999996</v>
+      </c>
+      <c r="P9" s="1">
+        <f>400.519-SUM(M9:O9)</f>
+        <v>86.149000000000001</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>78.751999999999995</v>
+      </c>
+      <c r="R9" s="1">
+        <v>69.173000000000002</v>
+      </c>
+      <c r="S9" s="1">
+        <v>29.72</v>
+      </c>
+      <c r="T9" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
@@ -1016,13 +1405,37 @@
       <c r="K10" s="3">
         <v>57.61</v>
       </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="L10" s="3">
+        <f>202.111-SUM(I10:K10)</f>
+        <v>49.322000000000003</v>
+      </c>
+      <c r="M10" s="3">
+        <v>47.308</v>
+      </c>
       <c r="N10" s="3">
         <v>59.936999999999998</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O10" s="1">
+        <v>64.622</v>
+      </c>
+      <c r="P10" s="1">
+        <f>229.379-SUM(M10:O10)</f>
+        <v>57.511999999999972</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>51.433</v>
+      </c>
+      <c r="R10" s="1">
+        <v>62.969000000000001</v>
+      </c>
+      <c r="S10" s="1">
+        <v>92.238</v>
+      </c>
+      <c r="T10" s="18">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
@@ -1051,13 +1464,122 @@
       <c r="K12" s="3">
         <v>555.12599999999998</v>
       </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
+      <c r="L12" s="3">
+        <f>2096.706-SUM(I12:K12)</f>
+        <v>597.29700000000003</v>
+      </c>
+      <c r="M12" s="3">
+        <v>650</v>
+      </c>
       <c r="N12" s="3">
         <v>711.19899999999996</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O12" s="1">
+        <v>760.68</v>
+      </c>
+      <c r="P12" s="1">
+        <f>2922.576-SUM(M12:O12)</f>
+        <v>800.69700000000012</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>851.98199999999997</v>
+      </c>
+      <c r="R12" s="1">
+        <v>932.18100000000004</v>
+      </c>
+      <c r="S12" s="1">
+        <v>1071.355</v>
+      </c>
+      <c r="T12" s="18"/>
+      <c r="V12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="W12" s="1">
+        <f>SUM(E15:H15)</f>
+        <v>2089.1320000000001</v>
+      </c>
+      <c r="X12" s="1">
+        <f>SUM(I15:L15)</f>
+        <v>2802.8820000000005</v>
+      </c>
+      <c r="Y12" s="1">
+        <f>SUM(M15:P15)</f>
+        <v>3534.6469999999999</v>
+      </c>
+      <c r="Z12" s="1">
+        <f>SUM(Q15:T15)</f>
+        <v>4354.518</v>
+      </c>
+      <c r="AA12" s="1">
+        <f>Z12*(1+AA13)</f>
+        <v>5356.0571399999999</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" ref="AB12:AQ12" si="0">AA12*(1+AB13)</f>
+        <v>6587.9502821999995</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" si="0"/>
+        <v>8103.178847105999</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" si="0"/>
+        <v>9966.9099819403782</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" si="0"/>
+        <v>12259.299277786666</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" si="0"/>
+        <v>15078.938111677598</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" si="0"/>
+        <v>18547.093877363444</v>
+      </c>
+      <c r="AH12" s="1">
+        <f t="shared" si="0"/>
+        <v>22812.925469157035</v>
+      </c>
+      <c r="AI12" s="1">
+        <f t="shared" si="0"/>
+        <v>28059.898327063154</v>
+      </c>
+      <c r="AJ12" s="1">
+        <f t="shared" si="0"/>
+        <v>34513.674942287682</v>
+      </c>
+      <c r="AK12" s="1">
+        <f t="shared" si="0"/>
+        <v>42451.820179013848</v>
+      </c>
+      <c r="AL12" s="1">
+        <f t="shared" si="0"/>
+        <v>52215.738820187034</v>
+      </c>
+      <c r="AM12" s="1">
+        <f t="shared" si="0"/>
+        <v>64225.358748830055</v>
+      </c>
+      <c r="AN12" s="1">
+        <f t="shared" si="0"/>
+        <v>78997.191261060972</v>
+      </c>
+      <c r="AO12" s="1">
+        <f t="shared" si="0"/>
+        <v>97166.545251104995</v>
+      </c>
+      <c r="AP12" s="1">
+        <f t="shared" si="0"/>
+        <v>119514.85065885914</v>
+      </c>
+      <c r="AQ12" s="1">
+        <f t="shared" si="0"/>
+        <v>147003.26631039675</v>
+      </c>
+    </row>
+    <row r="13" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1086,13 +1608,118 @@
       <c r="K13" s="3">
         <v>120.333</v>
       </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
+      <c r="L13" s="3">
+        <f>495.077-SUM(I13:K13)</f>
+        <v>117.09500000000003</v>
+      </c>
+      <c r="M13" s="3">
+        <v>113.565</v>
+      </c>
       <c r="N13" s="3">
         <v>106.023</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O13" s="1">
+        <v>94.224999999999994</v>
+      </c>
+      <c r="P13" s="1">
+        <f>399.738-SUM(M13:O13)</f>
+        <v>85.925000000000011</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>78.597999999999999</v>
+      </c>
+      <c r="R13" s="1">
+        <v>69.102000000000004</v>
+      </c>
+      <c r="S13" s="1">
+        <v>29.535</v>
+      </c>
+      <c r="T13" s="18"/>
+      <c r="V13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="X13" s="15">
+        <f>(X12-W12)/W12</f>
+        <v>0.34164906765106295</v>
+      </c>
+      <c r="Y13" s="15">
+        <f>(Y12-X12)/X12</f>
+        <v>0.26107592114116801</v>
+      </c>
+      <c r="Z13" s="15">
+        <f>(Z12-Y12)/Y12</f>
+        <v>0.23195272399195735</v>
+      </c>
+      <c r="AA13" s="15">
+        <f>$AB$22</f>
+        <v>0.23</v>
+      </c>
+      <c r="AB13" s="15">
+        <f t="shared" ref="AB13:AQ13" si="1">$AB$22</f>
+        <v>0.23</v>
+      </c>
+      <c r="AC13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AD13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AE13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AF13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AG13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AH13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AI13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AJ13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AK13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AL13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AM13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AN13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AO13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AP13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="AQ13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1123,61 +1750,109 @@
       <c r="K14" s="3">
         <v>65.031999999999996</v>
       </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+      <c r="L14" s="3">
+        <f>211.099-SUM(I14:K14)</f>
+        <v>45.449000000000012</v>
+      </c>
+      <c r="M14" s="3">
+        <v>42.843000000000004</v>
+      </c>
       <c r="N14" s="3">
         <v>55.481999999999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O14" s="1">
+        <v>60.548000000000002</v>
+      </c>
+      <c r="P14" s="1">
+        <f>212.333-SUM(M14:O14)</f>
+        <v>53.460000000000008</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>47.195</v>
+      </c>
+      <c r="R14" s="1">
+        <v>58.826999999999998</v>
+      </c>
+      <c r="S14" s="1">
+        <v>88.242999999999995</v>
+      </c>
+      <c r="T14" s="18"/>
+    </row>
+    <row r="15" spans="1:43" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9">
-        <f t="shared" ref="D15:K15" si="0">SUM(D12:D14)</f>
+        <f t="shared" ref="D15:M15" si="2">SUM(D12:D14)</f>
         <v>430.476</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>459.50600000000003</v>
       </c>
       <c r="F15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>501.35900000000004</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>568.72800000000007</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>559.53899999999999</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>614.024</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>688.52600000000007</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>740.49099999999999</v>
       </c>
       <c r="L15" s="9">
-        <v>759.8</v>
+        <f t="shared" si="2"/>
+        <v>759.84100000000012</v>
       </c>
       <c r="M15" s="9">
-        <v>807.4</v>
+        <f t="shared" si="2"/>
+        <v>806.40800000000002</v>
       </c>
       <c r="N15" s="9">
-        <f t="shared" ref="N15" si="1">SUM(N12:N14)</f>
+        <f t="shared" ref="N15:S15" si="3">SUM(N12:N14)</f>
         <v>872.70399999999995</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O15" s="9">
+        <f t="shared" si="3"/>
+        <v>915.45299999999997</v>
+      </c>
+      <c r="P15" s="9">
+        <f t="shared" si="3"/>
+        <v>940.08200000000011</v>
+      </c>
+      <c r="Q15" s="9">
+        <f t="shared" si="3"/>
+        <v>977.77499999999998</v>
+      </c>
+      <c r="R15" s="9">
+        <f t="shared" si="3"/>
+        <v>1060.1100000000001</v>
+      </c>
+      <c r="S15" s="9">
+        <f t="shared" si="3"/>
+        <v>1189.133</v>
+      </c>
+      <c r="T15" s="19">
+        <f>(1120+1135)/2</f>
+        <v>1127.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>13</v>
       </c>
@@ -1208,57 +1883,107 @@
         <f>119.374-5.709</f>
         <v>113.66499999999999</v>
       </c>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
+      <c r="L16" s="3">
+        <f>465.707-SUM(I16:K16)</f>
+        <v>138.863</v>
+      </c>
+      <c r="M16" s="3">
+        <v>139.392</v>
+      </c>
       <c r="N16" s="3">
         <f>N15-N17</f>
         <v>131.69499999999994</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O16" s="1">
+        <v>168.65199999999999</v>
+      </c>
+      <c r="P16" s="1">
+        <f>633.765-SUM(M16:O16)</f>
+        <v>194.02600000000007</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>178.029</v>
+      </c>
+      <c r="R16" s="1">
+        <v>194.536</v>
+      </c>
+      <c r="S16" s="1">
+        <f>213.425</f>
+        <v>213.42500000000001</v>
+      </c>
+      <c r="T16" s="18"/>
+    </row>
+    <row r="17" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3">
-        <f t="shared" ref="D17:K17" si="2">+D15-D16</f>
+        <f t="shared" ref="D17:M17" si="4">+D15-D16</f>
         <v>360.35500000000002</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>385.822</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>421.87700000000007</v>
       </c>
       <c r="G17" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>489.39400000000006</v>
       </c>
       <c r="H17" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>461.572</v>
       </c>
       <c r="I17" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>516.00599999999997</v>
       </c>
       <c r="J17" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>573.36500000000001</v>
       </c>
       <c r="K17" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>626.82600000000002</v>
       </c>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
+      <c r="L17" s="3">
+        <f t="shared" si="4"/>
+        <v>620.97800000000007</v>
+      </c>
+      <c r="M17" s="3">
+        <f t="shared" si="4"/>
+        <v>667.01600000000008</v>
+      </c>
       <c r="N17" s="3">
         <v>741.00900000000001</v>
       </c>
-    </row>
-    <row r="18" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O17" s="3">
+        <f t="shared" ref="O17:S17" si="5">+O15-O16</f>
+        <v>746.80099999999993</v>
+      </c>
+      <c r="P17" s="3">
+        <f t="shared" si="5"/>
+        <v>746.05600000000004</v>
+      </c>
+      <c r="Q17" s="3">
+        <f t="shared" si="5"/>
+        <v>799.74599999999998</v>
+      </c>
+      <c r="R17" s="3">
+        <f t="shared" si="5"/>
+        <v>865.57400000000007</v>
+      </c>
+      <c r="S17" s="3">
+        <f t="shared" si="5"/>
+        <v>975.70800000000008</v>
+      </c>
+      <c r="T17" s="18"/>
+    </row>
+    <row r="18" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>15</v>
       </c>
@@ -1287,13 +2012,35 @@
       <c r="K18" s="3">
         <v>363.74599999999998</v>
       </c>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
+      <c r="L18" s="3">
+        <f>1397.568-SUM(I18:K18)</f>
+        <v>379</v>
+      </c>
+      <c r="M18" s="3">
+        <v>399.00599999999997</v>
+      </c>
       <c r="N18" s="3">
         <v>473.67599999999999</v>
       </c>
-    </row>
-    <row r="19" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O18" s="1">
+        <v>522.34400000000005</v>
+      </c>
+      <c r="P18" s="1">
+        <f>1869.881-SUM(M18:O18)</f>
+        <v>474.85500000000002</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>481.738</v>
+      </c>
+      <c r="R18" s="1">
+        <v>536.779</v>
+      </c>
+      <c r="S18" s="1">
+        <v>576.49</v>
+      </c>
+      <c r="T18" s="18"/>
+    </row>
+    <row r="19" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
@@ -1324,13 +2071,35 @@
         <f>150.796-2.302</f>
         <v>148.494</v>
       </c>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
+      <c r="L19" s="3">
+        <f>567.691-SUM(I19:K19)</f>
+        <v>181.61</v>
+      </c>
+      <c r="M19" s="3">
+        <v>160.12799999999999</v>
+      </c>
       <c r="N19" s="3">
         <v>186.191</v>
       </c>
-    </row>
-    <row r="20" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O19" s="1">
+        <v>220.92099999999999</v>
+      </c>
+      <c r="P19" s="1">
+        <f>769.861-SUM(M19:O19)</f>
+        <v>202.62099999999998</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>193.56700000000001</v>
+      </c>
+      <c r="R19" s="1">
+        <v>220.51300000000001</v>
+      </c>
+      <c r="S19" s="1">
+        <v>223.81399999999999</v>
+      </c>
+      <c r="T19" s="18"/>
+    </row>
+    <row r="20" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>17</v>
       </c>
@@ -1359,27 +2128,49 @@
       <c r="K20" s="3">
         <v>122.70699999999999</v>
       </c>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
+      <c r="L20" s="3">
+        <f>478.373-SUM(I20:K20)</f>
+        <v>131.63200000000001</v>
+      </c>
+      <c r="M20" s="3">
+        <v>142.893</v>
+      </c>
       <c r="N20" s="3">
         <v>156.131</v>
       </c>
-    </row>
-    <row r="21" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O20" s="1">
+        <v>165.10300000000001</v>
+      </c>
+      <c r="P20" s="1">
+        <f>606.362-SUM(M20:O20)</f>
+        <v>142.23499999999996</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>143.31</v>
+      </c>
+      <c r="R20" s="1">
+        <v>157.34399999999999</v>
+      </c>
+      <c r="S20" s="1">
+        <v>157.595</v>
+      </c>
+      <c r="T20" s="18"/>
+    </row>
+    <row r="21" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3">
-        <f t="shared" ref="D21:F21" si="3">SUM(D18:D20)</f>
+        <f t="shared" ref="D21:F21" si="6">SUM(D18:D20)</f>
         <v>363.64400000000001</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>373.89</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>394.16399999999999</v>
       </c>
       <c r="G21" s="3">
@@ -1403,33 +2194,54 @@
         <v>634.947</v>
       </c>
       <c r="L21" s="3">
-        <f t="shared" ref="L21:N21" si="4">SUM(L18:L20)</f>
-        <v>0</v>
+        <f t="shared" ref="L21:S21" si="7">SUM(L18:L20)</f>
+        <v>692.24199999999996</v>
       </c>
       <c r="M21" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>702.02700000000004</v>
       </c>
       <c r="N21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>815.99799999999993</v>
       </c>
-    </row>
-    <row r="22" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O21" s="3">
+        <f t="shared" si="7"/>
+        <v>908.36800000000017</v>
+      </c>
+      <c r="P21" s="3">
+        <f t="shared" si="7"/>
+        <v>819.71100000000001</v>
+      </c>
+      <c r="Q21" s="3">
+        <f t="shared" si="7"/>
+        <v>818.61500000000001</v>
+      </c>
+      <c r="R21" s="3">
+        <f t="shared" si="7"/>
+        <v>914.63599999999997</v>
+      </c>
+      <c r="S21" s="3">
+        <f t="shared" si="7"/>
+        <v>957.899</v>
+      </c>
+      <c r="T21" s="18"/>
+    </row>
+    <row r="22" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3">
-        <f t="shared" ref="D22:F22" si="5">+D17-D21</f>
+        <f t="shared" ref="D22:F22" si="8">+D17-D21</f>
         <v>-3.2889999999999873</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>11.932000000000016</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>27.713000000000079</v>
       </c>
       <c r="G22" s="3">
@@ -1453,19 +2265,46 @@
         <v>-8.1209999999999809</v>
       </c>
       <c r="L22" s="3">
-        <f t="shared" ref="L22:N22" si="6">+L17-L21</f>
-        <v>0</v>
+        <f t="shared" ref="L22:N22" si="9">+L17-L21</f>
+        <v>-71.263999999999896</v>
       </c>
       <c r="M22" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>-35.010999999999967</v>
       </c>
       <c r="N22" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>-74.988999999999919</v>
       </c>
-    </row>
-    <row r="23" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <f>+O17-O21</f>
+        <v>-161.56700000000023</v>
+      </c>
+      <c r="P22" s="1">
+        <f>-345.22-SUM(M22:O22)</f>
+        <v>-73.652999999999906</v>
+      </c>
+      <c r="Q22" s="3">
+        <f>+Q17-Q21</f>
+        <v>-18.869000000000028</v>
+      </c>
+      <c r="R22" s="3">
+        <f>+R17-R21</f>
+        <v>-49.061999999999898</v>
+      </c>
+      <c r="S22" s="3">
+        <f>+S17-S21</f>
+        <v>17.809000000000083</v>
+      </c>
+      <c r="T22" s="18"/>
+      <c r="AA22" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB22" s="23">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="23" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
@@ -1501,64 +2340,124 @@
         <f>0.608-6.024</f>
         <v>-5.4160000000000004</v>
       </c>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
+      <c r="L23" s="3">
+        <f>-49.552-SUM(I23:K23)</f>
+        <v>-31.303999999999998</v>
+      </c>
+      <c r="M23" s="3">
+        <f>-6.121+5.143</f>
+        <v>-0.97800000000000065</v>
+      </c>
       <c r="N23" s="3">
         <f>-6.749+8.963-7.508</f>
         <v>-5.2940000000000005</v>
       </c>
-    </row>
-    <row r="24" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O23" s="1">
+        <f>15.047-7.978</f>
+        <v>7.0690000000000008</v>
+      </c>
+      <c r="P23" s="1">
+        <f>14.5-SUM(M23:O23)</f>
+        <v>13.702999999999999</v>
+      </c>
+      <c r="Q23" s="14">
+        <f>25.226-8.976</f>
+        <v>16.25</v>
+      </c>
+      <c r="R23" s="1">
+        <f>22.593-4.639</f>
+        <v>17.954000000000001</v>
+      </c>
+      <c r="S23" s="1">
+        <f>21.414-10.99</f>
+        <v>10.424000000000001</v>
+      </c>
+      <c r="T23" s="18"/>
+      <c r="AA23" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB23" s="23">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3">
-        <f t="shared" ref="D24:N24" si="7">+D22+D23</f>
+        <f t="shared" ref="D24:S24" si="10">+D22+D23</f>
         <v>-12.382999999999987</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1.9470000000000169</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>29.825000000000081</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>68.220000000000041</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>-14.617000000000012</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32.814999999999955</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>-72.718999999999966</v>
       </c>
       <c r="K24" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>-13.536999999999981</v>
       </c>
       <c r="L24" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-102.5679999999999</v>
       </c>
       <c r="M24" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-35.988999999999969</v>
       </c>
       <c r="N24" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>-80.282999999999916</v>
       </c>
-    </row>
-    <row r="25" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <f t="shared" si="10"/>
+        <v>-154.49800000000025</v>
+      </c>
+      <c r="P24" s="3">
+        <f t="shared" si="10"/>
+        <v>-59.949999999999903</v>
+      </c>
+      <c r="Q24" s="3">
+        <f t="shared" si="10"/>
+        <v>-2.6190000000000282</v>
+      </c>
+      <c r="R24" s="3">
+        <f t="shared" si="10"/>
+        <v>-31.107999999999898</v>
+      </c>
+      <c r="S24" s="3">
+        <f t="shared" si="10"/>
+        <v>28.233000000000082</v>
+      </c>
+      <c r="T24" s="18"/>
+      <c r="AA24" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB24" s="23">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="25" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>22</v>
       </c>
@@ -1587,112 +2486,201 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
+      <c r="L25" s="3">
+        <f>-49.552</f>
+        <v>-49.552</v>
+      </c>
+      <c r="M25" s="3">
+        <f>-8.025</f>
+        <v>-8.0250000000000004</v>
+      </c>
       <c r="N25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <f>-100.498</f>
+        <v>-100.498</v>
+      </c>
+      <c r="O25" s="1">
+        <v>53.595999999999997</v>
+      </c>
+      <c r="P25" s="1">
+        <f>-175.652-SUM(M25:O25)</f>
+        <v>-120.72499999999997</v>
+      </c>
+      <c r="Q25" s="1">
+        <f>-20.929</f>
+        <v>-20.928999999999998</v>
+      </c>
+      <c r="R25" s="1">
+        <f>-40.109</f>
+        <v>-40.109000000000002</v>
+      </c>
+      <c r="S25" s="1">
+        <f>-7.023</f>
+        <v>-7.0229999999999997</v>
+      </c>
+      <c r="T25" s="18"/>
+      <c r="AA25" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB25" s="24">
+        <f>NPV(AB24,W12:AQ12)</f>
+        <v>148579.65860454194</v>
+      </c>
+    </row>
+    <row r="26" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3">
-        <f t="shared" ref="D26:N26" si="8">+D24-D25</f>
+        <f t="shared" ref="D26:S26" si="11">+D24-D25</f>
         <v>-12.382999999999987</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1.9470000000000169</v>
       </c>
       <c r="F26" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>29.825000000000081</v>
       </c>
       <c r="G26" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>68.220000000000041</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-14.617000000000012</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>32.814999999999955</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-72.718999999999966</v>
       </c>
       <c r="K26" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-13.536999999999981</v>
       </c>
       <c r="L26" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>-53.015999999999899</v>
       </c>
       <c r="M26" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>-27.96399999999997</v>
       </c>
       <c r="N26" s="3">
-        <f t="shared" si="8"/>
-        <v>-80.282999999999916</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+        <f t="shared" si="11"/>
+        <v>20.215000000000089</v>
+      </c>
+      <c r="O26" s="3">
+        <f t="shared" si="11"/>
+        <v>-208.09400000000025</v>
+      </c>
+      <c r="P26" s="3">
+        <f t="shared" si="11"/>
+        <v>60.775000000000063</v>
+      </c>
+      <c r="Q26" s="3">
+        <f t="shared" si="11"/>
+        <v>18.30999999999997</v>
+      </c>
+      <c r="R26" s="3">
+        <f t="shared" si="11"/>
+        <v>9.0010000000001043</v>
+      </c>
+      <c r="S26" s="3">
+        <f t="shared" si="11"/>
+        <v>35.256000000000085</v>
+      </c>
+      <c r="T26" s="18"/>
+      <c r="AA26" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="25">
+        <f>Main!L3</f>
+        <v>259.71699999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D27" s="10">
-        <f t="shared" ref="D27:N27" si="9">+D26/D28</f>
+        <f t="shared" ref="D27:S27" si="12">+D26/D28</f>
         <v>-5.0152080321089906E-2</v>
       </c>
       <c r="E27" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>7.8503316331674181E-3</v>
       </c>
       <c r="F27" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.11968874905693726</v>
       </c>
       <c r="G27" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.26739518986547944</v>
       </c>
       <c r="H27" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-5.81738728986246E-2</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.13016350265364551</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-0.28747232764073355</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-5.3353460269664088E-2</v>
       </c>
-      <c r="L27" s="10" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M27" s="10" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
+      <c r="L27" s="10">
+        <f t="shared" si="12"/>
+        <v>-0.20929130874178836</v>
+      </c>
+      <c r="M27" s="10">
+        <f t="shared" si="12"/>
+        <v>-0.10959097375444306</v>
       </c>
       <c r="N27" s="10">
-        <f t="shared" si="9"/>
-        <v>-0.31375989744952559</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="12"/>
+        <v>7.9003728397571027E-2</v>
+      </c>
+      <c r="O27" s="10">
+        <f t="shared" si="12"/>
+        <v>-0.81025601090236643</v>
+      </c>
+      <c r="P27" s="10">
+        <f t="shared" si="12"/>
+        <v>0.23711798741353166</v>
+      </c>
+      <c r="Q27" s="10">
+        <f t="shared" si="12"/>
+        <v>7.0994583318793103E-2</v>
+      </c>
+      <c r="R27" s="10">
+        <f t="shared" si="12"/>
+        <v>3.4806516602797766E-2</v>
+      </c>
+      <c r="S27" s="10">
+        <f t="shared" si="12"/>
+        <v>0.13574775621156909</v>
+      </c>
+      <c r="AA27" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB27" s="26">
+        <f>AB25/AB26</f>
+        <v>572.08291565258321</v>
+      </c>
+    </row>
+    <row r="28" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
         <v>1</v>
       </c>
@@ -1721,13 +2709,49 @@
       <c r="K28" s="3">
         <v>253.72300000000001</v>
       </c>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
+      <c r="L28" s="3">
+        <v>253.31200000000001</v>
+      </c>
+      <c r="M28" s="3">
+        <v>255.167</v>
+      </c>
       <c r="N28" s="3">
         <v>255.874</v>
       </c>
-    </row>
-    <row r="30" spans="2:14" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O28" s="1">
+        <v>256.82499999999999</v>
+      </c>
+      <c r="P28" s="1">
+        <v>256.30700000000002</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>257.90699999999998</v>
+      </c>
+      <c r="R28" s="1">
+        <v>258.601</v>
+      </c>
+      <c r="S28" s="1">
+        <v>259.71699999999998</v>
+      </c>
+      <c r="T28" s="18"/>
+      <c r="AA28" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB28" s="27">
+        <f>(AB27-[1]Main!$L$2)/[1]Main!$L$2</f>
+        <v>-0.20764139106290413</v>
+      </c>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AA29" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB29" s="28">
+        <f>AB26*AB27</f>
+        <v>148579.65860454194</v>
+      </c>
+    </row>
+    <row r="30" spans="2:28" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="4" t="s">
         <v>12</v>
       </c>
@@ -1737,35 +2761,58 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="11">
-        <f>+H15/D15-1</f>
+        <f t="shared" ref="H30:S30" si="13">+H15/D15-1</f>
         <v>0.29981462381178048</v>
       </c>
       <c r="I30" s="11">
-        <f>+I15/E15-1</f>
+        <f t="shared" si="13"/>
         <v>0.33626982019821283</v>
       </c>
       <c r="J30" s="11">
-        <f>+J15/F15-1</f>
+        <f t="shared" si="13"/>
         <v>0.373319318093422</v>
       </c>
       <c r="K30" s="11">
-        <f>+K15/G15-1</f>
+        <f t="shared" si="13"/>
         <v>0.30201256136501087</v>
       </c>
       <c r="L30" s="11">
-        <f>+L15/H15-1</f>
-        <v>0.35790355989484191</v>
+        <f t="shared" si="13"/>
+        <v>0.35797683450125928</v>
       </c>
       <c r="M30" s="11">
-        <f>+M15/I15-1</f>
-        <v>0.31493231534923716</v>
+        <f t="shared" si="13"/>
+        <v>0.31331674331947945</v>
       </c>
       <c r="N30" s="11">
-        <f>+N15/J15-1</f>
+        <f t="shared" si="13"/>
         <v>0.26749607131756803</v>
       </c>
-    </row>
-    <row r="31" spans="2:14" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O30" s="11">
+        <f t="shared" si="13"/>
+        <v>0.23627836124949519</v>
+      </c>
+      <c r="P30" s="11">
+        <f t="shared" si="13"/>
+        <v>0.23720883711197471</v>
+      </c>
+      <c r="Q30" s="11">
+        <f t="shared" si="13"/>
+        <v>0.21250657235543291</v>
+      </c>
+      <c r="R30" s="11">
+        <f t="shared" si="13"/>
+        <v>0.21474176811381662</v>
+      </c>
+      <c r="S30" s="11">
+        <f>+S15/O15-1</f>
+        <v>0.29895581750237321</v>
+      </c>
+      <c r="T30" s="20">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="31" spans="2:28" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
         <v>45</v>
       </c>
@@ -1787,85 +2834,182 @@
         <f>+K7/G7-1</f>
         <v>0.59858571548629524</v>
       </c>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="L31" s="11" t="e">
+        <f>+L7/H7-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M31" s="11">
+        <f>+M12/I7-1</f>
+        <v>1.0446488394258626</v>
+      </c>
+      <c r="N31" s="11">
+        <f>+N7/J7-1</f>
+        <v>0.40713102755019936</v>
+      </c>
+      <c r="O31" s="11">
+        <f>+O7/K7-1</f>
+        <v>0.33905866272127128</v>
+      </c>
+      <c r="P31" s="11">
+        <f>+P7/L7-1</f>
+        <v>0.29785537676654328</v>
+      </c>
+      <c r="Q31" s="11">
+        <f>+Q7/M7-1</f>
+        <v>0.2728258283986924</v>
+      </c>
+      <c r="R31" s="11">
+        <f>+R7/N7-1</f>
+        <v>0.27496657460450691</v>
+      </c>
+      <c r="S31" s="11">
+        <f>+S7/O7-1</f>
+        <v>0.31435376553353866</v>
+      </c>
+      <c r="T31" s="21">
+        <f>+T7/P7-1</f>
+        <v>0.32000000000000006</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="6">
-        <f t="shared" ref="D32:K32" si="10">+D17/D15</f>
+        <f t="shared" ref="D32:S32" si="14">+D17/D15</f>
         <v>0.8371082243841701</v>
       </c>
       <c r="E32" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0.83964518417604983</v>
       </c>
       <c r="F32" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0.84146689298486721</v>
       </c>
       <c r="G32" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0.86050625254954916</v>
       </c>
       <c r="H32" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0.8249147959302211</v>
       </c>
       <c r="I32" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0.84036780321290372</v>
       </c>
       <c r="J32" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0.83274269962209113</v>
       </c>
       <c r="K32" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0.84650049764278035</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="L32" s="6">
+        <f t="shared" si="14"/>
+        <v>0.81724729252567307</v>
+      </c>
+      <c r="M32" s="6">
+        <f t="shared" si="14"/>
+        <v>0.8271445719784527</v>
+      </c>
+      <c r="N32" s="6">
+        <f t="shared" si="14"/>
+        <v>0.84909545504546791</v>
+      </c>
+      <c r="O32" s="6">
+        <f t="shared" si="14"/>
+        <v>0.81577208223688158</v>
+      </c>
+      <c r="P32" s="6">
+        <f t="shared" si="14"/>
+        <v>0.79360736616593019</v>
+      </c>
+      <c r="Q32" s="6">
+        <f t="shared" si="14"/>
+        <v>0.81792436910332134</v>
+      </c>
+      <c r="R32" s="6">
+        <f t="shared" si="14"/>
+        <v>0.81649451472017054</v>
+      </c>
+      <c r="S32" s="6">
+        <f t="shared" si="14"/>
+        <v>0.82052049686620421</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="6">
-        <f t="shared" ref="D33:K33" si="11">+D22/D15</f>
+        <f t="shared" ref="D33:S33" si="15">+D22/D15</f>
         <v>-7.640379486893549E-3</v>
       </c>
       <c r="E33" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>2.5967016752773665E-2</v>
       </c>
       <c r="F33" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>5.5275760483007343E-2</v>
       </c>
       <c r="G33" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0.13599998593352186</v>
       </c>
       <c r="H33" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-1.3450358241337978E-2</v>
       </c>
       <c r="I33" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>6.4567508761872436E-2</v>
       </c>
       <c r="J33" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-9.6899753967170377E-2</v>
       </c>
       <c r="K33" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-1.0967047540078111E-2</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="L33" s="6">
+        <f t="shared" si="15"/>
+        <v>-9.3788042498364643E-2</v>
+      </c>
+      <c r="M33" s="6">
+        <f t="shared" si="15"/>
+        <v>-4.341598793662757E-2</v>
+      </c>
+      <c r="N33" s="6">
+        <f t="shared" si="15"/>
+        <v>-8.5927187224992582E-2</v>
+      </c>
+      <c r="O33" s="6">
+        <f t="shared" si="15"/>
+        <v>-0.17648857997079068</v>
+      </c>
+      <c r="P33" s="6">
+        <f t="shared" si="15"/>
+        <v>-7.8347420756912589E-2</v>
+      </c>
+      <c r="Q33" s="6">
+        <f t="shared" si="15"/>
+        <v>-1.929789573265836E-2</v>
+      </c>
+      <c r="R33" s="6">
+        <f t="shared" si="15"/>
+        <v>-4.6280103008178294E-2</v>
+      </c>
+      <c r="S33" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4976457637623447E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>26</v>
       </c>
@@ -1897,8 +3041,10 @@
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
+      <c r="T37" s="18"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{8B4B4F9B-7A25-4B26-901F-5BB44EFDE58B}"/>
   </hyperlinks>

--- a/TEAM.xlsx
+++ b/TEAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A6FABA-BA3C-474C-BDCE-44AD61BD5CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD96AC8-719A-4985-B138-F9432890C992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27570" yWindow="7650" windowWidth="26610" windowHeight="13410" activeTab="1" xr2:uid="{3AF6BCC7-0372-4EF8-A651-596D3CC14EF5}"/>
+    <workbookView xWindow="14235" yWindow="90" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{3AF6BCC7-0372-4EF8-A651-596D3CC14EF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
   <si>
     <t>Price</t>
   </si>
@@ -299,20 +299,70 @@
     <t>WC</t>
   </si>
   <si>
-    <t>Q244</t>
-  </si>
-  <si>
     <t>TTM CFFO</t>
+  </si>
+  <si>
+    <t>FQ125</t>
+  </si>
+  <si>
+    <t>FQ225</t>
+  </si>
+  <si>
+    <t>FQ325</t>
+  </si>
+  <si>
+    <t>FQ425</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>YoY%</t>
+  </si>
+  <si>
+    <t>Growth Rate</t>
+  </si>
+  <si>
+    <t>Terminal Rate</t>
+  </si>
+  <si>
+    <t>Discount Rate</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Share Price</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>FCF</t>
+  </si>
+  <si>
+    <t>FCF Margin</t>
+  </si>
+  <si>
+    <t>FCF Yoy%</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -330,6 +380,12 @@
       <u/>
       <sz val="10"/>
       <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -351,11 +407,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -387,10 +445,16 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -419,7 +483,7 @@
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>17859</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>101203</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -787,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="13">
-        <v>309</v>
+        <v>149.52000000000001</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
@@ -798,11 +862,10 @@
         <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>260</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>78</v>
-      </c>
+        <f>Model!X28</f>
+        <v>261.78699999999998</v>
+      </c>
+      <c r="M3" s="3"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -813,7 +876,7 @@
       </c>
       <c r="L4" s="1">
         <f>+L2*L3</f>
-        <v>80340</v>
+        <v>39142.392240000001</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
@@ -824,22 +887,18 @@
         <v>3</v>
       </c>
       <c r="L5" s="1">
-        <v>2562</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>78</v>
-      </c>
+        <v>2512.8739999999998</v>
+      </c>
+      <c r="M5" s="3"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K6" t="s">
         <v>4</v>
       </c>
       <c r="L6" s="1">
-        <v>986</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>78</v>
-      </c>
+        <v>953.85699999999997</v>
+      </c>
+      <c r="M6" s="3"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K7" t="s">
@@ -847,7 +906,7 @@
       </c>
       <c r="L7" s="1">
         <f>+L4-L5+L6</f>
-        <v>78764</v>
+        <v>37583.375240000008</v>
       </c>
     </row>
   </sheetData>
@@ -857,7 +916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF29F7FA-B9F0-42C1-B494-BA78776DB519}">
-  <dimension ref="A1:X67"/>
+  <dimension ref="A1:CF69"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -868,9 +927,13 @@
     <col min="10" max="10" width="10.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="9.140625" style="2"/>
     <col min="16" max="20" width="9.5703125" customWidth="1"/>
+    <col min="28" max="28" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>6</v>
       </c>
@@ -938,7 +1001,7 @@
         <v>45838</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:84" x14ac:dyDescent="0.2">
       <c r="C2" s="2" t="s">
         <v>38</v>
       </c>
@@ -994,19 +1057,19 @@
         <v>53</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:84" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>45</v>
       </c>
@@ -1041,7 +1104,7 @@
         <v>253177</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:84" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
@@ -1084,7 +1147,7 @@
         <v>846.96199999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:84" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
@@ -1127,7 +1190,7 @@
         <v>362.28100000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:84" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
@@ -1164,7 +1227,7 @@
         <v>69.173000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:84" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
@@ -1206,8 +1269,280 @@
       <c r="V10" s="1">
         <v>77.22</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB10" s="15">
+        <v>2021</v>
+      </c>
+      <c r="AC10" s="15">
+        <v>2022</v>
+      </c>
+      <c r="AD10" s="15">
+        <v>2023</v>
+      </c>
+      <c r="AE10" s="15">
+        <v>2024</v>
+      </c>
+      <c r="AF10" s="15">
+        <v>2025</v>
+      </c>
+      <c r="AG10" s="15">
+        <v>2026</v>
+      </c>
+      <c r="AH10" s="15">
+        <v>2027</v>
+      </c>
+      <c r="AI10" s="15">
+        <v>2028</v>
+      </c>
+      <c r="AJ10" s="15">
+        <v>2029</v>
+      </c>
+      <c r="AK10" s="15">
+        <v>2030</v>
+      </c>
+      <c r="AL10" s="15">
+        <v>2031</v>
+      </c>
+      <c r="AM10" s="15">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="11" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="AA11" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB11" s="1">
+        <f>SUM(E15:H15)</f>
+        <v>2089.1320000000001</v>
+      </c>
+      <c r="AC11" s="1">
+        <f>SUM(I15:L15)</f>
+        <v>2802.8820000000001</v>
+      </c>
+      <c r="AD11" s="1">
+        <f>SUM(M15:P15)</f>
+        <v>3534.6469999999999</v>
+      </c>
+      <c r="AE11" s="1">
+        <f>SUM(Q15:T15)</f>
+        <v>4358.6030000000001</v>
+      </c>
+      <c r="AF11" s="1">
+        <f>SUM(U15:X15)</f>
+        <v>5215.3040000000001</v>
+      </c>
+      <c r="AG11">
+        <f>AF11*(1+$AC$22)</f>
+        <v>6154.05872</v>
+      </c>
+      <c r="AH11">
+        <f>AG11*(1+$AC$22)</f>
+        <v>7261.7892895999994</v>
+      </c>
+      <c r="AI11">
+        <f>AH11*(1+$AC$22)</f>
+        <v>8568.9113617279982</v>
+      </c>
+      <c r="AJ11">
+        <f>AI11*(1+$AC$22)</f>
+        <v>10111.315406839038</v>
+      </c>
+      <c r="AK11">
+        <f>AJ11*(1+$AC$22)</f>
+        <v>11931.352180070064</v>
+      </c>
+      <c r="AL11">
+        <f>AK11*(1+$AC$23)</f>
+        <v>12050.665701870765</v>
+      </c>
+      <c r="AM11">
+        <f>AL11*(1+$AC$23)</f>
+        <v>12171.172358889473</v>
+      </c>
+      <c r="AN11">
+        <f>AM11*(1+$AC$23)</f>
+        <v>12292.884082478367</v>
+      </c>
+      <c r="AO11">
+        <f>AN11*(1+$AC$23)</f>
+        <v>12415.81292330315</v>
+      </c>
+      <c r="AP11">
+        <f>AO11*(1+$AC$23)</f>
+        <v>12539.971052536182</v>
+      </c>
+      <c r="AQ11">
+        <f>AP11*(1+$AC$23)</f>
+        <v>12665.370763061544</v>
+      </c>
+      <c r="AR11">
+        <f>AQ11*(1+$AC$23)</f>
+        <v>12792.02447069216</v>
+      </c>
+      <c r="AS11">
+        <f>AR11*(1+$AC$23)</f>
+        <v>12919.944715399082</v>
+      </c>
+      <c r="AT11">
+        <f>AS11*(1+$AC$23)</f>
+        <v>13049.144162553073</v>
+      </c>
+      <c r="AU11">
+        <f>AT11*(1+$AC$23)</f>
+        <v>13179.635604178604</v>
+      </c>
+      <c r="AV11">
+        <f>AU11*(1+$AC$23)</f>
+        <v>13311.43196022039</v>
+      </c>
+      <c r="AW11">
+        <f>AV11*(1+$AC$23)</f>
+        <v>13444.546279822594</v>
+      </c>
+      <c r="AX11">
+        <f>AW11*(1+$AC$23)</f>
+        <v>13578.991742620821</v>
+      </c>
+      <c r="AY11">
+        <f>AX11*(1+$AC$23)</f>
+        <v>13714.781660047029</v>
+      </c>
+      <c r="AZ11">
+        <f>AY11*(1+$AC$23)</f>
+        <v>13851.9294766475</v>
+      </c>
+      <c r="BA11">
+        <f>AZ11*(1+$AC$23)</f>
+        <v>13990.448771413974</v>
+      </c>
+      <c r="BB11">
+        <f>BA11*(1+$AC$23)</f>
+        <v>14130.353259128115</v>
+      </c>
+      <c r="BC11">
+        <f>BB11*(1+$AC$23)</f>
+        <v>14271.656791719395</v>
+      </c>
+      <c r="BD11">
+        <f>BC11*(1+$AC$23)</f>
+        <v>14414.373359636589</v>
+      </c>
+      <c r="BE11">
+        <f>BD11*(1+$AC$23)</f>
+        <v>14558.517093232955</v>
+      </c>
+      <c r="BF11">
+        <f>BE11*(1+$AC$23)</f>
+        <v>14704.102264165285</v>
+      </c>
+      <c r="BG11">
+        <f>BF11*(1+$AC$23)</f>
+        <v>14851.143286806939</v>
+      </c>
+      <c r="BH11">
+        <f>BG11*(1+$AC$23)</f>
+        <v>14999.654719675009</v>
+      </c>
+      <c r="BI11">
+        <f>BH11*(1+$AC$23)</f>
+        <v>15149.651266871759</v>
+      </c>
+      <c r="BJ11">
+        <f>BI11*(1+$AC$23)</f>
+        <v>15301.147779540477</v>
+      </c>
+      <c r="BK11">
+        <f>BJ11*(1+$AC$23)</f>
+        <v>15454.159257335881</v>
+      </c>
+      <c r="BL11">
+        <f>BK11*(1+$AC$23)</f>
+        <v>15608.700849909241</v>
+      </c>
+      <c r="BM11">
+        <f>BL11*(1+$AC$23)</f>
+        <v>15764.787858408334</v>
+      </c>
+      <c r="BN11">
+        <f>BM11*(1+$AC$23)</f>
+        <v>15922.435736992416</v>
+      </c>
+      <c r="BO11">
+        <f>BN11*(1+$AC$23)</f>
+        <v>16081.660094362342</v>
+      </c>
+      <c r="BP11">
+        <f>BO11*(1+$AC$23)</f>
+        <v>16242.476695305964</v>
+      </c>
+      <c r="BQ11">
+        <f>BP11*(1+$AC$23)</f>
+        <v>16404.901462259026</v>
+      </c>
+      <c r="BR11">
+        <f>BQ11*(1+$AC$23)</f>
+        <v>16568.950476881615</v>
+      </c>
+      <c r="BS11">
+        <f>BR11*(1+$AC$23)</f>
+        <v>16734.639981650431</v>
+      </c>
+      <c r="BT11">
+        <f>BS11*(1+$AC$23)</f>
+        <v>16901.986381466937</v>
+      </c>
+      <c r="BU11">
+        <f>BT11*(1+$AC$23)</f>
+        <v>17071.006245281606</v>
+      </c>
+      <c r="BV11">
+        <f>BU11*(1+$AC$23)</f>
+        <v>17241.716307734423</v>
+      </c>
+      <c r="BW11">
+        <f>BV11*(1+$AC$23)</f>
+        <v>17414.133470811768</v>
+      </c>
+      <c r="BX11">
+        <f>BW11*(1+$AC$23)</f>
+        <v>17588.274805519886</v>
+      </c>
+      <c r="BY11">
+        <f>BX11*(1+$AC$23)</f>
+        <v>17764.157553575085</v>
+      </c>
+      <c r="BZ11">
+        <f>BY11*(1+$AC$23)</f>
+        <v>17941.799129110837</v>
+      </c>
+      <c r="CA11">
+        <f>BZ11*(1+$AC$23)</f>
+        <v>18121.217120401947</v>
+      </c>
+      <c r="CB11">
+        <f>CA11*(1+$AC$23)</f>
+        <v>18302.429291605968</v>
+      </c>
+      <c r="CC11">
+        <f>CB11*(1+$AC$23)</f>
+        <v>18485.453584522027</v>
+      </c>
+      <c r="CD11">
+        <f>CC11*(1+$AC$23)</f>
+        <v>18670.308120367248</v>
+      </c>
+      <c r="CE11">
+        <f>CD11*(1+$AC$23)</f>
+        <v>18857.01120157092</v>
+      </c>
+      <c r="CF11">
+        <f>CE11*(1+$AC$23)</f>
+        <v>19045.58131358663</v>
+      </c>
+    </row>
+    <row r="12" spans="1:84" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1269,8 +1604,54 @@
       <c r="V12" s="1">
         <v>1213.248</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W12" s="1">
+        <v>1272.876</v>
+      </c>
+      <c r="X12" s="9">
+        <f>4930.604-SUM(U12:W12)</f>
+        <v>1312.5320000000002</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC12" s="16">
+        <f>(AC11-AB11)/AB11</f>
+        <v>0.34164906765106273</v>
+      </c>
+      <c r="AD12" s="16">
+        <f>(AD11-AC11)/AC11</f>
+        <v>0.26107592114116823</v>
+      </c>
+      <c r="AE12" s="16">
+        <f>(AE11-AD11)/AD11</f>
+        <v>0.23310842638600124</v>
+      </c>
+      <c r="AF12" s="16">
+        <f>(AF11-AE11)/AE11</f>
+        <v>0.19655403348274667</v>
+      </c>
+      <c r="AG12" s="16">
+        <f>(AG11-AF11)/AF11</f>
+        <v>0.17999999999999997</v>
+      </c>
+      <c r="AH12" s="16">
+        <f>(AH11-AG11)/AG11</f>
+        <v>0.17999999999999991</v>
+      </c>
+      <c r="AI12" s="16">
+        <f>(AI11-AH11)/AH11</f>
+        <v>0.17999999999999985</v>
+      </c>
+      <c r="AJ12" s="16">
+        <f>(AJ11-AI11)/AI11</f>
+        <v>0.18</v>
+      </c>
+      <c r="AK12" s="16">
+        <f>(AK11-AJ11)/AJ11</f>
+        <v>0.17999999999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:84" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1323,8 +1704,14 @@
       <c r="S13" s="1">
         <v>29.53</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA13" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ13" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:84" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1388,8 +1775,238 @@
       <c r="V14" s="1">
         <v>73.215000000000003</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W14" s="1">
+        <v>83.84</v>
+      </c>
+      <c r="X14" s="1">
+        <f>284.7-SUM(U14:W14)</f>
+        <v>71.811999999999983</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>763.77099999999996</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>842.45899999999995</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>1415.5820000000001</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>1681</v>
+      </c>
+      <c r="AF14" s="1">
+        <f>SUM(U35:X35)</f>
+        <v>1415.5430000000001</v>
+      </c>
+      <c r="AG14" s="1">
+        <f>AG11*0.32</f>
+        <v>1969.2987904000001</v>
+      </c>
+      <c r="AH14" s="1">
+        <f>AH11*0.32</f>
+        <v>2323.772572672</v>
+      </c>
+      <c r="AI14" s="1">
+        <f>AI11*0.32</f>
+        <v>2742.0516357529596</v>
+      </c>
+      <c r="AJ14" s="1">
+        <f>AJ11*0.32</f>
+        <v>3235.6209301884919</v>
+      </c>
+      <c r="AK14">
+        <f>AJ14*(1+$AG$23)</f>
+        <v>3267.9771394903769</v>
+      </c>
+      <c r="AL14">
+        <f>AK14*(1+$AG$23)</f>
+        <v>3300.6569108852805</v>
+      </c>
+      <c r="AM14">
+        <f>AL14*(1+$AG$23)</f>
+        <v>3333.6634799941335</v>
+      </c>
+      <c r="AN14">
+        <f>AM14*(1+$AG$23)</f>
+        <v>3367.0001147940748</v>
+      </c>
+      <c r="AO14">
+        <f>AN14*(1+$AG$23)</f>
+        <v>3400.6701159420154</v>
+      </c>
+      <c r="AP14">
+        <f>AO14*(1+$AG$23)</f>
+        <v>3434.6768171014355</v>
+      </c>
+      <c r="AQ14">
+        <f>AP14*(1+$AG$23)</f>
+        <v>3469.02358527245</v>
+      </c>
+      <c r="AR14">
+        <f>AQ14*(1+$AG$23)</f>
+        <v>3503.7138211251745</v>
+      </c>
+      <c r="AS14">
+        <f>AR14*(1+$AG$23)</f>
+        <v>3538.7509593364261</v>
+      </c>
+      <c r="AT14">
+        <f>AS14*(1+$AG$23)</f>
+        <v>3574.1384689297906</v>
+      </c>
+      <c r="AU14">
+        <f>AT14*(1+$AG$23)</f>
+        <v>3609.8798536190884</v>
+      </c>
+      <c r="AV14">
+        <f>AU14*(1+$AG$23)</f>
+        <v>3645.9786521552792</v>
+      </c>
+      <c r="AW14">
+        <f>AV14*(1+$AG$23)</f>
+        <v>3682.438438676832</v>
+      </c>
+      <c r="AX14">
+        <f>AW14*(1+$AG$23)</f>
+        <v>3719.2628230636005</v>
+      </c>
+      <c r="AY14">
+        <f>AX14*(1+$AG$23)</f>
+        <v>3756.4554512942364</v>
+      </c>
+      <c r="AZ14">
+        <f>AY14*(1+$AG$23)</f>
+        <v>3794.0200058071787</v>
+      </c>
+      <c r="BA14">
+        <f>AZ14*(1+$AG$23)</f>
+        <v>3831.9602058652504</v>
+      </c>
+      <c r="BB14">
+        <f>BA14*(1+$AG$23)</f>
+        <v>3870.2798079239028</v>
+      </c>
+      <c r="BC14">
+        <f>BB14*(1+$AG$23)</f>
+        <v>3908.9826060031419</v>
+      </c>
+      <c r="BD14">
+        <f>BC14*(1+$AG$23)</f>
+        <v>3948.0724320631734</v>
+      </c>
+      <c r="BE14">
+        <f>BD14*(1+$AG$23)</f>
+        <v>3987.5531563838053</v>
+      </c>
+      <c r="BF14">
+        <f>BE14*(1+$AG$23)</f>
+        <v>4027.4286879476435</v>
+      </c>
+      <c r="BG14">
+        <f>BF14*(1+$AG$23)</f>
+        <v>4067.7029748271202</v>
+      </c>
+      <c r="BH14">
+        <f>BG14*(1+$AG$23)</f>
+        <v>4108.3800045753915</v>
+      </c>
+      <c r="BI14">
+        <f>BH14*(1+$AG$23)</f>
+        <v>4149.4638046211458</v>
+      </c>
+      <c r="BJ14">
+        <f>BI14*(1+$AG$23)</f>
+        <v>4190.9584426673573</v>
+      </c>
+      <c r="BK14">
+        <f>BJ14*(1+$AG$23)</f>
+        <v>4232.8680270940313</v>
+      </c>
+      <c r="BL14">
+        <f>BK14*(1+$AG$23)</f>
+        <v>4275.1967073649712</v>
+      </c>
+      <c r="BM14">
+        <f>BL14*(1+$AG$23)</f>
+        <v>4317.9486744386213</v>
+      </c>
+      <c r="BN14">
+        <f>BM14*(1+$AG$23)</f>
+        <v>4361.1281611830073</v>
+      </c>
+      <c r="BO14">
+        <f>BN14*(1+$AG$23)</f>
+        <v>4404.7394427948375</v>
+      </c>
+      <c r="BP14">
+        <f>BO14*(1+$AG$23)</f>
+        <v>4448.7868372227858</v>
+      </c>
+      <c r="BQ14">
+        <f>BP14*(1+$AG$23)</f>
+        <v>4493.274705595014</v>
+      </c>
+      <c r="BR14">
+        <f>BQ14*(1+$AG$23)</f>
+        <v>4538.2074526509641</v>
+      </c>
+      <c r="BS14">
+        <f>BR14*(1+$AG$23)</f>
+        <v>4583.5895271774734</v>
+      </c>
+      <c r="BT14">
+        <f>BS14*(1+$AG$23)</f>
+        <v>4629.4254224492479</v>
+      </c>
+      <c r="BU14">
+        <f>BT14*(1+$AG$23)</f>
+        <v>4675.7196766737407</v>
+      </c>
+      <c r="BV14">
+        <f>BU14*(1+$AG$23)</f>
+        <v>4722.4768734404779</v>
+      </c>
+      <c r="BW14">
+        <f>BV14*(1+$AG$23)</f>
+        <v>4769.7016421748831</v>
+      </c>
+      <c r="BX14">
+        <f>BW14*(1+$AG$23)</f>
+        <v>4817.3986585966322</v>
+      </c>
+      <c r="BY14">
+        <f>BX14*(1+$AG$23)</f>
+        <v>4865.5726451825985</v>
+      </c>
+      <c r="BZ14">
+        <f>BY14*(1+$AG$23)</f>
+        <v>4914.2283716344245</v>
+      </c>
+      <c r="CA14">
+        <f>BZ14*(1+$AG$23)</f>
+        <v>4963.3706553507691</v>
+      </c>
+      <c r="CB14">
+        <f>CA14*(1+$AG$23)</f>
+        <v>5013.0043619042772</v>
+      </c>
+      <c r="CC14">
+        <f>CB14*(1+$AG$23)</f>
+        <v>5063.1344055233203</v>
+      </c>
+      <c r="CD14">
+        <f>CC14*(1+$AG$23)</f>
+        <v>5113.7657495785534</v>
+      </c>
+      <c r="CE14">
+        <f>CD14*(1+$AG$23)</f>
+        <v>5164.9034070743392</v>
+      </c>
+    </row>
+    <row r="15" spans="1:84" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="8" t="s">
         <v>7</v>
       </c>
@@ -1472,14 +2089,38 @@
       </c>
       <c r="W15" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1356.7159999999999</v>
       </c>
       <c r="X15" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>1384.3440000000001</v>
+      </c>
+      <c r="AA15" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC15" s="16">
+        <f>(AC14-AB14)/AB14</f>
+        <v>0.10302564512137799</v>
+      </c>
+      <c r="AD15" s="16">
+        <f>(AD14-AC14)/AC14</f>
+        <v>0.68029779490752684</v>
+      </c>
+      <c r="AE15" s="16">
+        <f>(AE14-AD14)/AD14</f>
+        <v>0.1874974392158136</v>
+      </c>
+      <c r="AF15" s="16">
+        <f>(AF14-AE14)/AE14</f>
+        <v>-0.15791612135633545</v>
+      </c>
+      <c r="AG15" s="16">
+        <f>(AG14-AF14)/AF14</f>
+        <v>0.39119672832262953</v>
+      </c>
+      <c r="AH15" s="16"/>
+    </row>
+    <row r="16" spans="1:84" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
@@ -1544,8 +2185,55 @@
       <c r="V16" s="1">
         <v>223.12700000000001</v>
       </c>
-    </row>
-    <row r="17" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W16" s="1">
+        <v>219.67500000000001</v>
+      </c>
+      <c r="X16" s="1">
+        <f>894.851-SUM(U16:W16)</f>
+        <v>234.42500000000007</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC16" s="16">
+        <f>AC14/AC11</f>
+        <v>0.30056884306938358</v>
+      </c>
+      <c r="AD16" s="16">
+        <f>AD14/AD11</f>
+        <v>0.40048751685811912</v>
+      </c>
+      <c r="AE16" s="16">
+        <f>AE14/AE11</f>
+        <v>0.38567403362958269</v>
+      </c>
+      <c r="AF16" s="16">
+        <f>AF14/AF11</f>
+        <v>0.27142099482599674</v>
+      </c>
+      <c r="AG16" s="16">
+        <f>AG14/AG11</f>
+        <v>0.32</v>
+      </c>
+      <c r="AH16" s="16">
+        <f>AH14/AH11</f>
+        <v>0.32</v>
+      </c>
+      <c r="AI16" s="16">
+        <f>AI14/AI11</f>
+        <v>0.32</v>
+      </c>
+      <c r="AJ16" s="16">
+        <f>AJ14/AJ11</f>
+        <v>0.32</v>
+      </c>
+      <c r="AK16" s="16"/>
+      <c r="AL16" s="16"/>
+      <c r="AM16" s="16"/>
+      <c r="AN16" s="16"/>
+      <c r="AO16" s="16"/>
+    </row>
+    <row r="17" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
@@ -1625,8 +2313,16 @@
         <f>+V15-V16</f>
         <v>1063.336</v>
       </c>
-    </row>
-    <row r="18" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W17" s="1">
+        <f>+W15-W16</f>
+        <v>1137.0409999999999</v>
+      </c>
+      <c r="X17" s="1">
+        <f>+X15-X16</f>
+        <v>1149.9189999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>14</v>
       </c>
@@ -1688,8 +2384,15 @@
       <c r="V18" s="1">
         <v>680.21299999999997</v>
       </c>
-    </row>
-    <row r="19" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W18" s="1">
+        <v>685.32</v>
+      </c>
+      <c r="X18" s="1">
+        <f>2669.312-SUM(U18:W18)</f>
+        <v>700.67799999999988</v>
+      </c>
+    </row>
+    <row r="19" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>15</v>
       </c>
@@ -1753,8 +2456,15 @@
       <c r="V19" s="1">
         <v>271.89400000000001</v>
       </c>
-    </row>
-    <row r="20" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W19" s="1">
+        <v>295.83199999999999</v>
+      </c>
+      <c r="X19" s="1">
+        <f>1134.535-SUM(U19:W19)</f>
+        <v>314.41600000000005</v>
+      </c>
+    </row>
+    <row r="20" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>16</v>
       </c>
@@ -1816,8 +2526,15 @@
       <c r="V20" s="1">
         <v>168.708</v>
       </c>
-    </row>
-    <row r="21" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W20" s="1">
+        <v>168.345</v>
+      </c>
+      <c r="X20" s="1">
+        <f>646.998-SUM(U20:W20)</f>
+        <v>163.30400000000009</v>
+      </c>
+    </row>
+    <row r="21" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>17</v>
       </c>
@@ -1867,7 +2584,7 @@
         <v>815.99799999999993</v>
       </c>
       <c r="O21" s="1">
-        <f t="shared" ref="O21:V21" si="8">SUM(O18:O20)</f>
+        <f t="shared" ref="O21:X21" si="8">SUM(O18:O20)</f>
         <v>908.36800000000017</v>
       </c>
       <c r="P21" s="1">
@@ -1898,8 +2615,16 @@
         <f t="shared" si="8"/>
         <v>1120.8150000000001</v>
       </c>
-    </row>
-    <row r="22" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W21" s="1">
+        <f t="shared" si="8"/>
+        <v>1149.4970000000001</v>
+      </c>
+      <c r="X21" s="1">
+        <f t="shared" si="8"/>
+        <v>1178.3980000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
@@ -1949,7 +2674,7 @@
         <v>-74.988999999999919</v>
       </c>
       <c r="O22" s="1">
-        <f t="shared" ref="O22:V22" si="11">+O17-O21</f>
+        <f t="shared" ref="O22:X22" si="11">+O17-O21</f>
         <v>-161.56700000000023</v>
       </c>
       <c r="P22" s="1">
@@ -1980,8 +2705,32 @@
         <f t="shared" si="11"/>
         <v>-57.479000000000042</v>
       </c>
-    </row>
-    <row r="23" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W22" s="1">
+        <f t="shared" si="11"/>
+        <v>-12.456000000000131</v>
+      </c>
+      <c r="X22" s="1">
+        <f t="shared" si="11"/>
+        <v>-28.479000000000269</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC22" s="16">
+        <v>0.18</v>
+      </c>
+      <c r="AE22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG22" s="16"/>
+    </row>
+    <row r="23" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>23</v>
       </c>
@@ -2061,8 +2810,28 @@
         <f>-7.999+25.586-7.291</f>
         <v>10.295999999999999</v>
       </c>
-    </row>
-    <row r="24" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W23" s="1">
+        <f>27.767-14.861-7.804</f>
+        <v>5.1019999999999985</v>
+      </c>
+      <c r="X23" s="1">
+        <f>112.324-30.55-50.277</f>
+        <v>31.497</v>
+      </c>
+      <c r="AB23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC23" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="AF23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG23" s="16">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="24" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
@@ -2143,8 +2912,28 @@
         <f>+V22+V23</f>
         <v>-47.183000000000042</v>
       </c>
-    </row>
-    <row r="25" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W24" s="1">
+        <f>+W22+W23</f>
+        <v>-7.3540000000001324</v>
+      </c>
+      <c r="X24" s="1">
+        <f>+X22+X23</f>
+        <v>3.0179999999997307</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC24" s="16">
+        <v>0.09</v>
+      </c>
+      <c r="AF24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG24" s="16">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="25" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>21</v>
       </c>
@@ -2206,8 +2995,29 @@
       <c r="V25" s="1">
         <v>-8.9749999999999996</v>
       </c>
-    </row>
-    <row r="26" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W25" s="1">
+        <v>-63.453000000000003</v>
+      </c>
+      <c r="X25" s="1">
+        <f>-157.782+SUM(U25:W25)</f>
+        <v>-136.60500000000002</v>
+      </c>
+      <c r="AB25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC25" s="17">
+        <f>NPV(AC24,AB11:CF11)</f>
+        <v>96980.510516830196</v>
+      </c>
+      <c r="AF25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG25" s="18">
+        <f>NPV(AG24,AE14:CJ14)</f>
+        <v>33292.14877462099</v>
+      </c>
+    </row>
+    <row r="26" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>20</v>
       </c>
@@ -2288,8 +3098,30 @@
         <f>+V24-V25</f>
         <v>-38.208000000000041</v>
       </c>
-    </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="1">
+        <f>+W24-W25</f>
+        <v>56.098999999999869</v>
+      </c>
+      <c r="X26" s="1">
+        <f>+X24-X25</f>
+        <v>139.62299999999976</v>
+      </c>
+      <c r="AB26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="1">
+        <f>X28</f>
+        <v>261.78699999999998</v>
+      </c>
+      <c r="AF26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="1">
+        <f>AC26</f>
+        <v>261.78699999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
         <v>24</v>
       </c>
@@ -2338,7 +3170,7 @@
         <v>-0.31375989744952559</v>
       </c>
       <c r="O27" s="13">
-        <f t="shared" ref="O27:V27" si="17">+O26/O28</f>
+        <f t="shared" ref="O27:X27" si="17">+O26/O28</f>
         <v>-0.81392777182906739</v>
       </c>
       <c r="P27" s="13">
@@ -2369,8 +3201,33 @@
         <f t="shared" si="17"/>
         <v>-0.14630840101552015</v>
       </c>
-    </row>
-    <row r="28" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W27" s="13">
+        <f t="shared" si="17"/>
+        <v>0.21357134971123523</v>
+      </c>
+      <c r="X27" s="13">
+        <f t="shared" si="17"/>
+        <v>0.53334581167131967</v>
+      </c>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC27" s="17">
+        <f>AC25/AC26</f>
+        <v>370.45579236872038</v>
+      </c>
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG27" s="17">
+        <f>AG25/AG26</f>
+        <v>127.1726585912249</v>
+      </c>
+    </row>
+    <row r="28" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
         <v>1</v>
       </c>
@@ -2432,8 +3289,28 @@
       <c r="V28" s="1">
         <v>261.14699999999999</v>
       </c>
-    </row>
-    <row r="30" spans="2:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W28" s="1">
+        <v>262.67099999999999</v>
+      </c>
+      <c r="X28" s="1">
+        <v>261.78699999999998</v>
+      </c>
+      <c r="AB28" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC28" s="16">
+        <f>(AC27-Main!L2)/Main!L2</f>
+        <v>1.4776337103311956</v>
+      </c>
+      <c r="AF28" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG28" s="16">
+        <f>(AG27-Main!L2)/Main!L2</f>
+        <v>-0.14946054981791804</v>
+      </c>
+    </row>
+    <row r="30" spans="2:33" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="4" t="s">
         <v>11</v>
       </c>
@@ -2443,7 +3320,7 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="11">
-        <f t="shared" ref="H30:V30" si="18">+H15/D15-1</f>
+        <f t="shared" ref="H30:X30" si="18">+H15/D15-1</f>
         <v>0.29981462381178048</v>
       </c>
       <c r="I30" s="11">
@@ -2502,8 +3379,16 @@
         <f t="shared" si="18"/>
         <v>0.21351840846704562</v>
       </c>
-    </row>
-    <row r="31" spans="2:22" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W30" s="11">
+        <f t="shared" si="18"/>
+        <v>0.1409335243977099</v>
+      </c>
+      <c r="X30" s="11">
+        <f t="shared" si="18"/>
+        <v>0.22336181832642543</v>
+      </c>
+    </row>
+    <row r="31" spans="2:33" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
         <v>44</v>
       </c>
@@ -2529,7 +3414,7 @@
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>13</v>
       </c>
@@ -2566,7 +3451,7 @@
         <v>0.84650049764278035</v>
       </c>
       <c r="L32" s="6">
-        <f t="shared" ref="L32:V32" si="20">+L17/L15</f>
+        <f t="shared" ref="L32:W32" si="20">+L17/L15</f>
         <v>0.82837988473904411</v>
       </c>
       <c r="M32" s="6">
@@ -2609,8 +3494,12 @@
         <f t="shared" si="20"/>
         <v>0.82655777896449412</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="6">
+        <f t="shared" si="20"/>
+        <v>0.8380832834579971</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>19</v>
       </c>
@@ -2647,7 +3536,7 @@
         <v>-1.0967047540078111E-2</v>
       </c>
       <c r="L33" s="6">
-        <f t="shared" ref="L33:V33" si="22">+L22/L15</f>
+        <f t="shared" ref="L33:W33" si="22">+L22/L15</f>
         <v>-5.5712971529569964E-2</v>
       </c>
       <c r="M33" s="6">
@@ -2690,329 +3579,378 @@
         <f t="shared" si="22"/>
         <v>-4.4679870311077771E-2</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="6">
+        <f t="shared" si="22"/>
+        <v>-9.1809929270386219E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6"/>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
+        <v>92</v>
+      </c>
+      <c r="U35">
+        <v>74.340999999999994</v>
+      </c>
+      <c r="V35">
+        <v>342.56900000000002</v>
+      </c>
+      <c r="W35">
+        <v>638.31500000000005</v>
+      </c>
+      <c r="X35">
+        <v>360.31799999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="U36" s="16"/>
+      <c r="V36" s="16"/>
+      <c r="W36" s="16"/>
+      <c r="X36" s="16"/>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
         <v>3</v>
       </c>
-      <c r="T35" s="1">
+      <c r="T37" s="1">
         <f>2176.93+161.973+223.221</f>
         <v>2562.1239999999998</v>
       </c>
     </row>
-    <row r="36" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
         <v>54</v>
       </c>
-      <c r="T36" s="1">
+      <c r="T38" s="1">
         <v>628.04899999999998</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
         <v>55</v>
       </c>
-      <c r="T37" s="1">
+      <c r="T39" s="1">
         <v>109.312</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
         <v>56</v>
       </c>
-      <c r="T38" s="1">
+      <c r="T40" s="1">
         <v>86.314999999999998</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
         <v>57</v>
       </c>
-      <c r="T39" s="1">
+      <c r="T41" s="1">
         <v>172.46799999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
         <v>58</v>
       </c>
-      <c r="T40" s="1">
+      <c r="T42" s="1">
         <f>299.057+1288.756</f>
         <v>1587.8130000000001</v>
       </c>
     </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
         <v>59</v>
       </c>
-      <c r="T41" s="1">
+      <c r="T43" s="1">
         <v>3.9340000000000002</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
         <v>60</v>
       </c>
-      <c r="T42" s="1">
+      <c r="T44" s="1">
         <v>62.118000000000002</v>
       </c>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
         <v>61</v>
       </c>
-      <c r="T43" s="1">
-        <f>SUM(T35:T42)</f>
+      <c r="T45" s="1">
+        <f>SUM(T37:T44)</f>
         <v>5212.1330000000007</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="T44" s="1"/>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="T46" s="1"/>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
         <v>62</v>
       </c>
-      <c r="T45" s="1">
+      <c r="T47" s="1">
         <v>177.54499999999999</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
         <v>63</v>
       </c>
-      <c r="T46" s="1">
+      <c r="T48" s="1">
         <v>577.35900000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
+    <row r="49" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
         <v>64</v>
       </c>
-      <c r="T47" s="1">
+      <c r="T49" s="1">
         <f>1806.269+308.467</f>
         <v>2114.7359999999999</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
+    <row r="50" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
         <v>57</v>
       </c>
-      <c r="T48" s="1">
+      <c r="T50" s="1">
         <f>48.953+214.474</f>
         <v>263.42700000000002</v>
       </c>
     </row>
-    <row r="49" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B49" t="s">
-        <v>4</v>
-      </c>
-      <c r="T49" s="1">
-        <v>985.91099999999994</v>
-      </c>
-    </row>
-    <row r="50" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B50" t="s">
-        <v>59</v>
-      </c>
-      <c r="T50" s="1">
-        <v>20.387</v>
-      </c>
-    </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="T51" s="1">
-        <v>39.917000000000002</v>
+        <v>985.91099999999994</v>
       </c>
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="T52" s="1">
-        <v>1032.8510000000001</v>
+        <v>20.387</v>
       </c>
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T53" s="1">
-        <f>SUM(T45:T52)</f>
-        <v>5212.1329999999998</v>
+        <v>39.917000000000002</v>
       </c>
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="T54" s="1"/>
+      <c r="B54" t="s">
+        <v>66</v>
+      </c>
+      <c r="T54" s="1">
+        <v>1032.8510000000001</v>
+      </c>
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
+        <v>65</v>
+      </c>
+      <c r="T55" s="1">
+        <f>SUM(T47:T54)</f>
+        <v>5212.1329999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T56" s="1"/>
+    </row>
+    <row r="57" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
         <v>68</v>
       </c>
-      <c r="T55" s="1">
+      <c r="T57" s="1">
         <f>+T26</f>
         <v>-196.91899999999993</v>
       </c>
     </row>
-    <row r="56" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B56" t="s">
-        <v>69</v>
-      </c>
-      <c r="T56" s="1">
-        <v>-196.91900000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
-        <v>70</v>
-      </c>
-      <c r="T57" s="1">
-        <v>23.178000000000001</v>
-      </c>
-    </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="T58" s="1">
-        <v>273.488</v>
+        <v>-196.91900000000001</v>
       </c>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T59" s="1">
-        <v>0.217</v>
+        <v>23.178000000000001</v>
       </c>
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T60" s="1">
-        <v>0.56599999999999995</v>
+        <v>273.488</v>
       </c>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T61" s="1">
-        <v>-4.1660000000000004</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="T62" s="1">
-        <v>1.587</v>
+        <v>0.56599999999999995</v>
       </c>
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="T63" s="1">
-        <v>2.1589999999999998</v>
+        <v>-4.1660000000000004</v>
       </c>
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T64" s="1">
-        <v>4.1000000000000002E-2</v>
+        <v>1.587</v>
       </c>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
+        <v>76</v>
+      </c>
+      <c r="T65" s="1">
+        <v>2.1589999999999998</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>10</v>
+      </c>
+      <c r="T66" s="1">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
         <v>77</v>
       </c>
-      <c r="T65" s="1">
+      <c r="T67" s="1">
         <f>18.025+56.406-10.7+103.165+159.172</f>
         <v>326.06799999999998</v>
       </c>
     </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B66" t="s">
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B68" t="s">
         <v>25</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D68" s="3">
         <v>123.34099999999999</v>
       </c>
-      <c r="E66" s="3">
+      <c r="E68" s="3">
         <v>79.465000000000003</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F68" s="3">
         <v>200.46199999999999</v>
       </c>
-      <c r="G66" s="3">
+      <c r="G68" s="3">
         <v>377.036</v>
       </c>
-      <c r="H66" s="3">
+      <c r="H68" s="3">
         <v>184.36699999999999</v>
       </c>
-      <c r="I66" s="3">
+      <c r="I68" s="3">
         <v>78.385999999999996</v>
       </c>
-      <c r="J66" s="3">
+      <c r="J68" s="3">
         <v>221.684</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K68" s="3">
         <v>353.029</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M68" s="3">
         <v>92.441999999999993</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N68" s="3">
         <v>150.52500000000001</v>
       </c>
-      <c r="O66" s="1">
+      <c r="O68" s="1">
         <v>352.36900000000003</v>
       </c>
-      <c r="P66" s="1">
+      <c r="P68" s="1">
         <v>272.77499999999998</v>
       </c>
-      <c r="Q66" s="1">
+      <c r="Q68" s="1">
         <v>166.95599999999999</v>
       </c>
-      <c r="R66" s="1">
+      <c r="R68" s="1">
         <v>289.59399999999999</v>
       </c>
-      <c r="S66" s="1">
+      <c r="S68" s="1">
         <v>565.39</v>
       </c>
-      <c r="T66" s="1">
-        <f>SUM(T56:T65)</f>
+      <c r="T68" s="1">
+        <f>SUM(T58:T67)</f>
         <v>426.21899999999999</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B67" t="s">
-        <v>79</v>
-      </c>
-      <c r="P67" s="1">
-        <f>SUM(M66:P66)</f>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>78</v>
+      </c>
+      <c r="P69" s="1">
+        <f>SUM(M68:P68)</f>
         <v>868.11099999999999</v>
       </c>
-      <c r="Q67" s="1">
-        <f>SUM(N66:Q66)</f>
+      <c r="Q69" s="1">
+        <f>SUM(N68:Q68)</f>
         <v>942.625</v>
       </c>
-      <c r="R67" s="1">
-        <f>SUM(O66:R66)</f>
+      <c r="R69" s="1">
+        <f>SUM(O68:R68)</f>
         <v>1081.694</v>
       </c>
-      <c r="S67" s="1">
-        <f>SUM(P66:S66)</f>
+      <c r="S69" s="1">
+        <f>SUM(P68:S68)</f>
         <v>1294.7150000000001</v>
       </c>
-      <c r="T67" s="1">
-        <f>SUM(Q66:T66)</f>
+      <c r="T69" s="1">
+        <f>SUM(Q68:T68)</f>
         <v>1448.1589999999999</v>
       </c>
     </row>

--- a/TEAM.xlsx
+++ b/TEAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD96AC8-719A-4985-B138-F9432890C992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA214D4-7CDB-424B-BC87-DA5190A86426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14235" yWindow="90" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{3AF6BCC7-0372-4EF8-A651-596D3CC14EF5}"/>
+    <workbookView xWindow="16035" yWindow="90" windowWidth="24390" windowHeight="20805" activeTab="1" xr2:uid="{3AF6BCC7-0372-4EF8-A651-596D3CC14EF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="98">
   <si>
     <t>Price</t>
   </si>
@@ -351,6 +351,12 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>FQ126</t>
+  </si>
+  <si>
+    <t>Sub % QoQ</t>
   </si>
 </sst>
 </file>
@@ -413,7 +419,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -445,10 +451,15 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -851,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="13">
-        <v>149.52000000000001</v>
+        <v>169.42</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
@@ -876,7 +887,7 @@
       </c>
       <c r="L4" s="1">
         <f>+L2*L3</f>
-        <v>39142.392240000001</v>
+        <v>44351.953539999995</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
@@ -887,7 +898,7 @@
         <v>3</v>
       </c>
       <c r="L5" s="1">
-        <v>2512.8739999999998</v>
+        <v>2778</v>
       </c>
       <c r="M5" s="3"/>
     </row>
@@ -896,7 +907,7 @@
         <v>4</v>
       </c>
       <c r="L6" s="1">
-        <v>953.85699999999997</v>
+        <v>1230</v>
       </c>
       <c r="M6" s="3"/>
     </row>
@@ -906,7 +917,7 @@
       </c>
       <c r="L7" s="1">
         <f>+L4-L5+L6</f>
-        <v>37583.375240000008</v>
+        <v>42803.953539999995</v>
       </c>
     </row>
   </sheetData>
@@ -927,6 +938,7 @@
     <col min="10" max="10" width="10.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="9.140625" style="2"/>
     <col min="16" max="20" width="9.5703125" customWidth="1"/>
+    <col min="25" max="25" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -1000,6 +1012,9 @@
       <c r="X1" s="14">
         <v>45838</v>
       </c>
+      <c r="Y1" s="18">
+        <v>45961</v>
+      </c>
     </row>
     <row r="2" spans="1:84" x14ac:dyDescent="0.2">
       <c r="C2" s="2" t="s">
@@ -1067,6 +1082,9 @@
       </c>
       <c r="X2" s="2" t="s">
         <v>82</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:84" x14ac:dyDescent="0.2">
@@ -1272,44 +1290,71 @@
       <c r="AA10" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AB10" s="15">
+      <c r="AB10">
         <v>2021</v>
       </c>
-      <c r="AC10" s="15">
+      <c r="AC10">
         <v>2022</v>
       </c>
-      <c r="AD10" s="15">
+      <c r="AD10">
         <v>2023</v>
       </c>
-      <c r="AE10" s="15">
+      <c r="AE10">
         <v>2024</v>
       </c>
-      <c r="AF10" s="15">
+      <c r="AF10">
         <v>2025</v>
       </c>
-      <c r="AG10" s="15">
+      <c r="AG10">
         <v>2026</v>
       </c>
-      <c r="AH10" s="15">
+      <c r="AH10">
         <v>2027</v>
       </c>
-      <c r="AI10" s="15">
+      <c r="AI10">
         <v>2028</v>
       </c>
-      <c r="AJ10" s="15">
+      <c r="AJ10">
         <v>2029</v>
       </c>
-      <c r="AK10" s="15">
+      <c r="AK10">
         <v>2030</v>
       </c>
-      <c r="AL10" s="15">
+      <c r="AL10">
         <v>2031</v>
       </c>
-      <c r="AM10" s="15">
+      <c r="AM10">
         <v>2032</v>
       </c>
     </row>
     <row r="11" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="T11" s="19">
+        <f>(T12-S12)/S12</f>
+        <v>-2.318559207732193E-3</v>
+      </c>
+      <c r="U11" s="19">
+        <f>(U12-T12)/T12</f>
+        <v>5.9012733996899526E-2</v>
+      </c>
+      <c r="V11" s="19">
+        <f>(V12-U12)/U12</f>
+        <v>7.1823087279627634E-2</v>
+      </c>
+      <c r="W11" s="19">
+        <f>(W12-V12)/V12</f>
+        <v>4.9147412565279255E-2</v>
+      </c>
+      <c r="X11" s="19">
+        <f>(X12-W12)/W12</f>
+        <v>3.1154645071476073E-2</v>
+      </c>
+      <c r="Y11" s="19">
+        <f>(Y12-X12)/X12</f>
+        <v>4.7214086970831792E-2</v>
+      </c>
       <c r="AA11" t="s">
         <v>7</v>
       </c>
@@ -1335,211 +1380,211 @@
       </c>
       <c r="AG11">
         <f>AF11*(1+$AC$22)</f>
-        <v>6154.05872</v>
+        <v>6258.3648000000003</v>
       </c>
       <c r="AH11">
         <f>AG11*(1+$AC$22)</f>
-        <v>7261.7892895999994</v>
+        <v>7510.0377600000002</v>
       </c>
       <c r="AI11">
         <f>AH11*(1+$AC$22)</f>
-        <v>8568.9113617279982</v>
+        <v>9012.0453120000002</v>
       </c>
       <c r="AJ11">
         <f>AI11*(1+$AC$22)</f>
-        <v>10111.315406839038</v>
+        <v>10814.4543744</v>
       </c>
       <c r="AK11">
         <f>AJ11*(1+$AC$22)</f>
-        <v>11931.352180070064</v>
+        <v>12977.345249280001</v>
       </c>
       <c r="AL11">
-        <f>AK11*(1+$AC$23)</f>
-        <v>12050.665701870765</v>
+        <f t="shared" ref="AL11:CF11" si="0">AK11*(1+$AC$23)</f>
+        <v>13107.118701772801</v>
       </c>
       <c r="AM11">
-        <f>AL11*(1+$AC$23)</f>
-        <v>12171.172358889473</v>
+        <f t="shared" si="0"/>
+        <v>13238.189888790528</v>
       </c>
       <c r="AN11">
-        <f>AM11*(1+$AC$23)</f>
-        <v>12292.884082478367</v>
+        <f t="shared" si="0"/>
+        <v>13370.571787678433</v>
       </c>
       <c r="AO11">
-        <f>AN11*(1+$AC$23)</f>
-        <v>12415.81292330315</v>
+        <f t="shared" si="0"/>
+        <v>13504.277505555217</v>
       </c>
       <c r="AP11">
-        <f>AO11*(1+$AC$23)</f>
-        <v>12539.971052536182</v>
+        <f t="shared" si="0"/>
+        <v>13639.320280610769</v>
       </c>
       <c r="AQ11">
-        <f>AP11*(1+$AC$23)</f>
-        <v>12665.370763061544</v>
+        <f t="shared" si="0"/>
+        <v>13775.713483416877</v>
       </c>
       <c r="AR11">
-        <f>AQ11*(1+$AC$23)</f>
-        <v>12792.02447069216</v>
+        <f t="shared" si="0"/>
+        <v>13913.470618251045</v>
       </c>
       <c r="AS11">
-        <f>AR11*(1+$AC$23)</f>
-        <v>12919.944715399082</v>
+        <f t="shared" si="0"/>
+        <v>14052.605324433556</v>
       </c>
       <c r="AT11">
-        <f>AS11*(1+$AC$23)</f>
-        <v>13049.144162553073</v>
+        <f t="shared" si="0"/>
+        <v>14193.131377677892</v>
       </c>
       <c r="AU11">
-        <f>AT11*(1+$AC$23)</f>
-        <v>13179.635604178604</v>
+        <f t="shared" si="0"/>
+        <v>14335.06269145467</v>
       </c>
       <c r="AV11">
-        <f>AU11*(1+$AC$23)</f>
-        <v>13311.43196022039</v>
+        <f t="shared" si="0"/>
+        <v>14478.413318369217</v>
       </c>
       <c r="AW11">
-        <f>AV11*(1+$AC$23)</f>
-        <v>13444.546279822594</v>
+        <f t="shared" si="0"/>
+        <v>14623.197451552909</v>
       </c>
       <c r="AX11">
-        <f>AW11*(1+$AC$23)</f>
-        <v>13578.991742620821</v>
+        <f t="shared" si="0"/>
+        <v>14769.429426068438</v>
       </c>
       <c r="AY11">
-        <f>AX11*(1+$AC$23)</f>
-        <v>13714.781660047029</v>
+        <f t="shared" si="0"/>
+        <v>14917.123720329122</v>
       </c>
       <c r="AZ11">
-        <f>AY11*(1+$AC$23)</f>
-        <v>13851.9294766475</v>
+        <f t="shared" si="0"/>
+        <v>15066.294957532413</v>
       </c>
       <c r="BA11">
-        <f>AZ11*(1+$AC$23)</f>
-        <v>13990.448771413974</v>
+        <f t="shared" si="0"/>
+        <v>15216.957907107737</v>
       </c>
       <c r="BB11">
-        <f>BA11*(1+$AC$23)</f>
-        <v>14130.353259128115</v>
+        <f t="shared" si="0"/>
+        <v>15369.127486178815</v>
       </c>
       <c r="BC11">
-        <f>BB11*(1+$AC$23)</f>
-        <v>14271.656791719395</v>
+        <f t="shared" si="0"/>
+        <v>15522.818761040604</v>
       </c>
       <c r="BD11">
-        <f>BC11*(1+$AC$23)</f>
-        <v>14414.373359636589</v>
+        <f t="shared" si="0"/>
+        <v>15678.04694865101</v>
       </c>
       <c r="BE11">
-        <f>BD11*(1+$AC$23)</f>
-        <v>14558.517093232955</v>
+        <f t="shared" si="0"/>
+        <v>15834.82741813752</v>
       </c>
       <c r="BF11">
-        <f>BE11*(1+$AC$23)</f>
-        <v>14704.102264165285</v>
+        <f t="shared" si="0"/>
+        <v>15993.175692318895</v>
       </c>
       <c r="BG11">
-        <f>BF11*(1+$AC$23)</f>
-        <v>14851.143286806939</v>
+        <f t="shared" si="0"/>
+        <v>16153.107449242085</v>
       </c>
       <c r="BH11">
-        <f>BG11*(1+$AC$23)</f>
-        <v>14999.654719675009</v>
+        <f t="shared" si="0"/>
+        <v>16314.638523734506</v>
       </c>
       <c r="BI11">
-        <f>BH11*(1+$AC$23)</f>
-        <v>15149.651266871759</v>
+        <f t="shared" si="0"/>
+        <v>16477.784908971851</v>
       </c>
       <c r="BJ11">
-        <f>BI11*(1+$AC$23)</f>
-        <v>15301.147779540477</v>
+        <f t="shared" si="0"/>
+        <v>16642.562758061569</v>
       </c>
       <c r="BK11">
-        <f>BJ11*(1+$AC$23)</f>
-        <v>15454.159257335881</v>
+        <f t="shared" si="0"/>
+        <v>16808.988385642184</v>
       </c>
       <c r="BL11">
-        <f>BK11*(1+$AC$23)</f>
-        <v>15608.700849909241</v>
+        <f t="shared" si="0"/>
+        <v>16977.078269498605</v>
       </c>
       <c r="BM11">
-        <f>BL11*(1+$AC$23)</f>
-        <v>15764.787858408334</v>
+        <f t="shared" si="0"/>
+        <v>17146.849052193589</v>
       </c>
       <c r="BN11">
-        <f>BM11*(1+$AC$23)</f>
-        <v>15922.435736992416</v>
+        <f t="shared" si="0"/>
+        <v>17318.317542715526</v>
       </c>
       <c r="BO11">
-        <f>BN11*(1+$AC$23)</f>
-        <v>16081.660094362342</v>
+        <f t="shared" si="0"/>
+        <v>17491.500718142681</v>
       </c>
       <c r="BP11">
-        <f>BO11*(1+$AC$23)</f>
-        <v>16242.476695305964</v>
+        <f t="shared" si="0"/>
+        <v>17666.415725324106</v>
       </c>
       <c r="BQ11">
-        <f>BP11*(1+$AC$23)</f>
-        <v>16404.901462259026</v>
+        <f t="shared" si="0"/>
+        <v>17843.079882577349</v>
       </c>
       <c r="BR11">
-        <f>BQ11*(1+$AC$23)</f>
-        <v>16568.950476881615</v>
+        <f t="shared" si="0"/>
+        <v>18021.510681403124</v>
       </c>
       <c r="BS11">
-        <f>BR11*(1+$AC$23)</f>
-        <v>16734.639981650431</v>
+        <f t="shared" si="0"/>
+        <v>18201.725788217154</v>
       </c>
       <c r="BT11">
-        <f>BS11*(1+$AC$23)</f>
-        <v>16901.986381466937</v>
+        <f t="shared" si="0"/>
+        <v>18383.743046099327</v>
       </c>
       <c r="BU11">
-        <f>BT11*(1+$AC$23)</f>
-        <v>17071.006245281606</v>
+        <f t="shared" si="0"/>
+        <v>18567.580476560321</v>
       </c>
       <c r="BV11">
-        <f>BU11*(1+$AC$23)</f>
-        <v>17241.716307734423</v>
+        <f t="shared" si="0"/>
+        <v>18753.256281325925</v>
       </c>
       <c r="BW11">
-        <f>BV11*(1+$AC$23)</f>
-        <v>17414.133470811768</v>
+        <f t="shared" si="0"/>
+        <v>18940.788844139184</v>
       </c>
       <c r="BX11">
-        <f>BW11*(1+$AC$23)</f>
-        <v>17588.274805519886</v>
+        <f t="shared" si="0"/>
+        <v>19130.196732580574</v>
       </c>
       <c r="BY11">
-        <f>BX11*(1+$AC$23)</f>
-        <v>17764.157553575085</v>
+        <f t="shared" si="0"/>
+        <v>19321.49869990638</v>
       </c>
       <c r="BZ11">
-        <f>BY11*(1+$AC$23)</f>
-        <v>17941.799129110837</v>
+        <f t="shared" si="0"/>
+        <v>19514.713686905445</v>
       </c>
       <c r="CA11">
-        <f>BZ11*(1+$AC$23)</f>
-        <v>18121.217120401947</v>
+        <f t="shared" si="0"/>
+        <v>19709.860823774499</v>
       </c>
       <c r="CB11">
-        <f>CA11*(1+$AC$23)</f>
-        <v>18302.429291605968</v>
+        <f t="shared" si="0"/>
+        <v>19906.959432012245</v>
       </c>
       <c r="CC11">
-        <f>CB11*(1+$AC$23)</f>
-        <v>18485.453584522027</v>
+        <f t="shared" si="0"/>
+        <v>20106.029026332366</v>
       </c>
       <c r="CD11">
-        <f>CC11*(1+$AC$23)</f>
-        <v>18670.308120367248</v>
+        <f t="shared" si="0"/>
+        <v>20307.089316595691</v>
       </c>
       <c r="CE11">
-        <f>CD11*(1+$AC$23)</f>
-        <v>18857.01120157092</v>
+        <f t="shared" si="0"/>
+        <v>20510.160209761649</v>
       </c>
       <c r="CF11">
-        <f>CE11*(1+$AC$23)</f>
-        <v>19045.58131358663</v>
+        <f t="shared" si="0"/>
+        <v>20715.261811859265</v>
       </c>
     </row>
     <row r="12" spans="1:84" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -1611,44 +1656,47 @@
         <f>4930.604-SUM(U12:W12)</f>
         <v>1312.5320000000002</v>
       </c>
+      <c r="Y12" s="1">
+        <v>1374.502</v>
+      </c>
       <c r="AA12" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AC12" s="16">
-        <f>(AC11-AB11)/AB11</f>
+      <c r="AC12" s="15">
+        <f t="shared" ref="AC12:AK12" si="1">(AC11-AB11)/AB11</f>
         <v>0.34164906765106273</v>
       </c>
-      <c r="AD12" s="16">
-        <f>(AD11-AC11)/AC11</f>
+      <c r="AD12" s="15">
+        <f t="shared" si="1"/>
         <v>0.26107592114116823</v>
       </c>
-      <c r="AE12" s="16">
-        <f>(AE11-AD11)/AD11</f>
+      <c r="AE12" s="15">
+        <f t="shared" si="1"/>
         <v>0.23310842638600124</v>
       </c>
-      <c r="AF12" s="16">
-        <f>(AF11-AE11)/AE11</f>
+      <c r="AF12" s="15">
+        <f t="shared" si="1"/>
         <v>0.19655403348274667</v>
       </c>
-      <c r="AG12" s="16">
-        <f>(AG11-AF11)/AF11</f>
-        <v>0.17999999999999997</v>
-      </c>
-      <c r="AH12" s="16">
-        <f>(AH11-AG11)/AG11</f>
-        <v>0.17999999999999991</v>
-      </c>
-      <c r="AI12" s="16">
-        <f>(AI11-AH11)/AH11</f>
-        <v>0.17999999999999985</v>
-      </c>
-      <c r="AJ12" s="16">
-        <f>(AJ11-AI11)/AI11</f>
-        <v>0.18</v>
-      </c>
-      <c r="AK12" s="16">
-        <f>(AK11-AJ11)/AJ11</f>
-        <v>0.17999999999999994</v>
+      <c r="AG12" s="15">
+        <f t="shared" si="1"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="AH12" s="15">
+        <f t="shared" si="1"/>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="AI12" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="AJ12" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="AK12" s="15">
+        <f t="shared" si="1"/>
+        <v>0.20000000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:84" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -1782,6 +1830,9 @@
         <f>284.7-SUM(U14:W14)</f>
         <v>71.811999999999983</v>
       </c>
+      <c r="Y14" s="1">
+        <v>58.051000000000002</v>
+      </c>
       <c r="AA14" s="1" t="s">
         <v>92</v>
       </c>
@@ -1803,207 +1854,207 @@
       </c>
       <c r="AG14" s="1">
         <f>AG11*0.32</f>
-        <v>1969.2987904000001</v>
+        <v>2002.6767360000001</v>
       </c>
       <c r="AH14" s="1">
         <f>AH11*0.32</f>
-        <v>2323.772572672</v>
+        <v>2403.2120832000001</v>
       </c>
       <c r="AI14" s="1">
         <f>AI11*0.32</f>
-        <v>2742.0516357529596</v>
+        <v>2883.8544998400002</v>
       </c>
       <c r="AJ14" s="1">
         <f>AJ11*0.32</f>
-        <v>3235.6209301884919</v>
+        <v>3460.6253998080001</v>
       </c>
       <c r="AK14">
-        <f>AJ14*(1+$AG$23)</f>
-        <v>3267.9771394903769</v>
+        <f t="shared" ref="AK14:CE14" si="2">AJ14*(1+$AG$23)</f>
+        <v>3495.23165380608</v>
       </c>
       <c r="AL14">
-        <f>AK14*(1+$AG$23)</f>
-        <v>3300.6569108852805</v>
+        <f t="shared" si="2"/>
+        <v>3530.183970344141</v>
       </c>
       <c r="AM14">
-        <f>AL14*(1+$AG$23)</f>
-        <v>3333.6634799941335</v>
+        <f t="shared" si="2"/>
+        <v>3565.4858100475826</v>
       </c>
       <c r="AN14">
-        <f>AM14*(1+$AG$23)</f>
-        <v>3367.0001147940748</v>
+        <f t="shared" si="2"/>
+        <v>3601.1406681480585</v>
       </c>
       <c r="AO14">
-        <f>AN14*(1+$AG$23)</f>
-        <v>3400.6701159420154</v>
+        <f t="shared" si="2"/>
+        <v>3637.1520748295393</v>
       </c>
       <c r="AP14">
-        <f>AO14*(1+$AG$23)</f>
-        <v>3434.6768171014355</v>
+        <f t="shared" si="2"/>
+        <v>3673.5235955778348</v>
       </c>
       <c r="AQ14">
-        <f>AP14*(1+$AG$23)</f>
-        <v>3469.02358527245</v>
+        <f t="shared" si="2"/>
+        <v>3710.2588315336134</v>
       </c>
       <c r="AR14">
-        <f>AQ14*(1+$AG$23)</f>
-        <v>3503.7138211251745</v>
+        <f t="shared" si="2"/>
+        <v>3747.3614198489495</v>
       </c>
       <c r="AS14">
-        <f>AR14*(1+$AG$23)</f>
-        <v>3538.7509593364261</v>
+        <f t="shared" si="2"/>
+        <v>3784.835034047439</v>
       </c>
       <c r="AT14">
-        <f>AS14*(1+$AG$23)</f>
-        <v>3574.1384689297906</v>
+        <f t="shared" si="2"/>
+        <v>3822.6833843879135</v>
       </c>
       <c r="AU14">
-        <f>AT14*(1+$AG$23)</f>
-        <v>3609.8798536190884</v>
+        <f t="shared" si="2"/>
+        <v>3860.9102182317929</v>
       </c>
       <c r="AV14">
-        <f>AU14*(1+$AG$23)</f>
-        <v>3645.9786521552792</v>
+        <f t="shared" si="2"/>
+        <v>3899.519320414111</v>
       </c>
       <c r="AW14">
-        <f>AV14*(1+$AG$23)</f>
-        <v>3682.438438676832</v>
+        <f t="shared" si="2"/>
+        <v>3938.5145136182523</v>
       </c>
       <c r="AX14">
-        <f>AW14*(1+$AG$23)</f>
-        <v>3719.2628230636005</v>
+        <f t="shared" si="2"/>
+        <v>3977.8996587544348</v>
       </c>
       <c r="AY14">
-        <f>AX14*(1+$AG$23)</f>
-        <v>3756.4554512942364</v>
+        <f t="shared" si="2"/>
+        <v>4017.6786553419793</v>
       </c>
       <c r="AZ14">
-        <f>AY14*(1+$AG$23)</f>
-        <v>3794.0200058071787</v>
+        <f t="shared" si="2"/>
+        <v>4057.8554418953991</v>
       </c>
       <c r="BA14">
-        <f>AZ14*(1+$AG$23)</f>
-        <v>3831.9602058652504</v>
+        <f t="shared" si="2"/>
+        <v>4098.433996314353</v>
       </c>
       <c r="BB14">
-        <f>BA14*(1+$AG$23)</f>
-        <v>3870.2798079239028</v>
+        <f t="shared" si="2"/>
+        <v>4139.4183362774966</v>
       </c>
       <c r="BC14">
-        <f>BB14*(1+$AG$23)</f>
-        <v>3908.9826060031419</v>
+        <f t="shared" si="2"/>
+        <v>4180.8125196402716</v>
       </c>
       <c r="BD14">
-        <f>BC14*(1+$AG$23)</f>
-        <v>3948.0724320631734</v>
+        <f t="shared" si="2"/>
+        <v>4222.6206448366747</v>
       </c>
       <c r="BE14">
-        <f>BD14*(1+$AG$23)</f>
-        <v>3987.5531563838053</v>
+        <f t="shared" si="2"/>
+        <v>4264.8468512850413</v>
       </c>
       <c r="BF14">
-        <f>BE14*(1+$AG$23)</f>
-        <v>4027.4286879476435</v>
+        <f t="shared" si="2"/>
+        <v>4307.4953197978921</v>
       </c>
       <c r="BG14">
-        <f>BF14*(1+$AG$23)</f>
-        <v>4067.7029748271202</v>
+        <f t="shared" si="2"/>
+        <v>4350.5702729958712</v>
       </c>
       <c r="BH14">
-        <f>BG14*(1+$AG$23)</f>
-        <v>4108.3800045753915</v>
+        <f t="shared" si="2"/>
+        <v>4394.0759757258302</v>
       </c>
       <c r="BI14">
-        <f>BH14*(1+$AG$23)</f>
-        <v>4149.4638046211458</v>
+        <f t="shared" si="2"/>
+        <v>4438.0167354830883</v>
       </c>
       <c r="BJ14">
-        <f>BI14*(1+$AG$23)</f>
-        <v>4190.9584426673573</v>
+        <f t="shared" si="2"/>
+        <v>4482.3969028379188</v>
       </c>
       <c r="BK14">
-        <f>BJ14*(1+$AG$23)</f>
-        <v>4232.8680270940313</v>
+        <f t="shared" si="2"/>
+        <v>4527.2208718662978</v>
       </c>
       <c r="BL14">
-        <f>BK14*(1+$AG$23)</f>
-        <v>4275.1967073649712</v>
+        <f t="shared" si="2"/>
+        <v>4572.4930805849608</v>
       </c>
       <c r="BM14">
-        <f>BL14*(1+$AG$23)</f>
-        <v>4317.9486744386213</v>
+        <f t="shared" si="2"/>
+        <v>4618.2180113908107</v>
       </c>
       <c r="BN14">
-        <f>BM14*(1+$AG$23)</f>
-        <v>4361.1281611830073</v>
+        <f t="shared" si="2"/>
+        <v>4664.4001915047193</v>
       </c>
       <c r="BO14">
-        <f>BN14*(1+$AG$23)</f>
-        <v>4404.7394427948375</v>
+        <f t="shared" si="2"/>
+        <v>4711.0441934197661</v>
       </c>
       <c r="BP14">
-        <f>BO14*(1+$AG$23)</f>
-        <v>4448.7868372227858</v>
+        <f t="shared" si="2"/>
+        <v>4758.1546353539634</v>
       </c>
       <c r="BQ14">
-        <f>BP14*(1+$AG$23)</f>
-        <v>4493.274705595014</v>
+        <f t="shared" si="2"/>
+        <v>4805.7361817075034</v>
       </c>
       <c r="BR14">
-        <f>BQ14*(1+$AG$23)</f>
-        <v>4538.2074526509641</v>
+        <f t="shared" si="2"/>
+        <v>4853.7935435245781</v>
       </c>
       <c r="BS14">
-        <f>BR14*(1+$AG$23)</f>
-        <v>4583.5895271774734</v>
+        <f t="shared" si="2"/>
+        <v>4902.3314789598244</v>
       </c>
       <c r="BT14">
-        <f>BS14*(1+$AG$23)</f>
-        <v>4629.4254224492479</v>
+        <f t="shared" si="2"/>
+        <v>4951.3547937494222</v>
       </c>
       <c r="BU14">
-        <f>BT14*(1+$AG$23)</f>
-        <v>4675.7196766737407</v>
+        <f t="shared" si="2"/>
+        <v>5000.8683416869162</v>
       </c>
       <c r="BV14">
-        <f>BU14*(1+$AG$23)</f>
-        <v>4722.4768734404779</v>
+        <f t="shared" si="2"/>
+        <v>5050.8770251037859</v>
       </c>
       <c r="BW14">
-        <f>BV14*(1+$AG$23)</f>
-        <v>4769.7016421748831</v>
+        <f t="shared" si="2"/>
+        <v>5101.385795354824</v>
       </c>
       <c r="BX14">
-        <f>BW14*(1+$AG$23)</f>
-        <v>4817.3986585966322</v>
+        <f t="shared" si="2"/>
+        <v>5152.3996533083728</v>
       </c>
       <c r="BY14">
-        <f>BX14*(1+$AG$23)</f>
-        <v>4865.5726451825985</v>
+        <f t="shared" si="2"/>
+        <v>5203.9236498414566</v>
       </c>
       <c r="BZ14">
-        <f>BY14*(1+$AG$23)</f>
-        <v>4914.2283716344245</v>
+        <f t="shared" si="2"/>
+        <v>5255.9628863398711</v>
       </c>
       <c r="CA14">
-        <f>BZ14*(1+$AG$23)</f>
-        <v>4963.3706553507691</v>
+        <f t="shared" si="2"/>
+        <v>5308.5225152032699</v>
       </c>
       <c r="CB14">
-        <f>CA14*(1+$AG$23)</f>
-        <v>5013.0043619042772</v>
+        <f t="shared" si="2"/>
+        <v>5361.6077403553027</v>
       </c>
       <c r="CC14">
-        <f>CB14*(1+$AG$23)</f>
-        <v>5063.1344055233203</v>
+        <f t="shared" si="2"/>
+        <v>5415.2238177588561</v>
       </c>
       <c r="CD14">
-        <f>CC14*(1+$AG$23)</f>
-        <v>5113.7657495785534</v>
+        <f t="shared" si="2"/>
+        <v>5469.3760559364446</v>
       </c>
       <c r="CE14">
-        <f>CD14*(1+$AG$23)</f>
-        <v>5164.9034070743392</v>
+        <f t="shared" si="2"/>
+        <v>5524.0698164958094</v>
       </c>
     </row>
     <row r="15" spans="1:84" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2012,35 +2063,35 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9">
-        <f t="shared" ref="D15:K15" si="0">SUM(D12:D14)</f>
+        <f t="shared" ref="D15:K15" si="3">SUM(D12:D14)</f>
         <v>430.476</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>459.50600000000003</v>
       </c>
       <c r="F15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>501.35900000000004</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>568.72800000000007</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>559.53899999999999</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>614.024</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>688.52600000000007</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>740.49099999999999</v>
       </c>
       <c r="L15" s="9">
@@ -2048,77 +2099,81 @@
         <v>759.84100000000001</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" ref="M15:X15" si="1">SUM(M12:M14)</f>
+        <f t="shared" ref="M15:X15" si="4">SUM(M12:M14)</f>
         <v>807.39199999999994</v>
       </c>
       <c r="N15" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>872.70399999999995</v>
       </c>
       <c r="O15" s="9">
-        <f t="shared" ref="O15:P15" si="2">SUM(O12:O14)</f>
+        <f t="shared" ref="O15:P15" si="5">SUM(O12:O14)</f>
         <v>915.45299999999997</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>939.09799999999996</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>977.77499999999998</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" ref="R15:S15" si="3">SUM(R12:R14)</f>
+        <f t="shared" ref="R15:S15" si="6">SUM(R12:R14)</f>
         <v>1060.1100000000001</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1189.1279999999999</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1131.5900000000001</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1187.7810000000002</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1286.463</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1356.7159999999999</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1384.3440000000001</v>
+      </c>
+      <c r="Y15" s="8">
+        <f>SUM(Y14,Y12)</f>
+        <v>1432.5529999999999</v>
       </c>
       <c r="AA15" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="AC15" s="16">
+      <c r="AC15" s="15">
         <f>(AC14-AB14)/AB14</f>
         <v>0.10302564512137799</v>
       </c>
-      <c r="AD15" s="16">
+      <c r="AD15" s="15">
         <f>(AD14-AC14)/AC14</f>
         <v>0.68029779490752684</v>
       </c>
-      <c r="AE15" s="16">
+      <c r="AE15" s="15">
         <f>(AE14-AD14)/AD14</f>
         <v>0.1874974392158136</v>
       </c>
-      <c r="AF15" s="16">
+      <c r="AF15" s="15">
         <f>(AF14-AE14)/AE14</f>
         <v>-0.15791612135633545</v>
       </c>
-      <c r="AG15" s="16">
+      <c r="AG15" s="15">
         <f>(AG14-AF14)/AF14</f>
-        <v>0.39119672832262953</v>
-      </c>
-      <c r="AH15" s="16"/>
+        <v>0.41477633388741986</v>
+      </c>
+      <c r="AH15" s="15"/>
     </row>
     <row r="16" spans="1:84" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -2192,46 +2247,49 @@
         <f>894.851-SUM(U16:W16)</f>
         <v>234.42500000000007</v>
       </c>
+      <c r="Y16" s="1">
+        <v>257.92399999999998</v>
+      </c>
       <c r="AA16" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AC16" s="16">
-        <f>AC14/AC11</f>
+      <c r="AC16" s="15">
+        <f t="shared" ref="AC16:AJ16" si="7">AC14/AC11</f>
         <v>0.30056884306938358</v>
       </c>
-      <c r="AD16" s="16">
-        <f>AD14/AD11</f>
+      <c r="AD16" s="15">
+        <f t="shared" si="7"/>
         <v>0.40048751685811912</v>
       </c>
-      <c r="AE16" s="16">
-        <f>AE14/AE11</f>
+      <c r="AE16" s="15">
+        <f t="shared" si="7"/>
         <v>0.38567403362958269</v>
       </c>
-      <c r="AF16" s="16">
-        <f>AF14/AF11</f>
+      <c r="AF16" s="15">
+        <f t="shared" si="7"/>
         <v>0.27142099482599674</v>
       </c>
-      <c r="AG16" s="16">
-        <f>AG14/AG11</f>
+      <c r="AG16" s="15">
+        <f t="shared" si="7"/>
         <v>0.32</v>
       </c>
-      <c r="AH16" s="16">
-        <f>AH14/AH11</f>
+      <c r="AH16" s="15">
+        <f t="shared" si="7"/>
         <v>0.32</v>
       </c>
-      <c r="AI16" s="16">
-        <f>AI14/AI11</f>
+      <c r="AI16" s="15">
+        <f t="shared" si="7"/>
         <v>0.32</v>
       </c>
-      <c r="AJ16" s="16">
-        <f>AJ14/AJ11</f>
+      <c r="AJ16" s="15">
+        <f t="shared" si="7"/>
         <v>0.32</v>
       </c>
-      <c r="AK16" s="16"/>
-      <c r="AL16" s="16"/>
-      <c r="AM16" s="16"/>
-      <c r="AN16" s="16"/>
-      <c r="AO16" s="16"/>
+      <c r="AK16" s="15"/>
+      <c r="AL16" s="15"/>
+      <c r="AM16" s="15"/>
+      <c r="AN16" s="15"/>
+      <c r="AO16" s="15"/>
     </row>
     <row r="17" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
@@ -2239,35 +2297,35 @@
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3">
-        <f t="shared" ref="D17:K17" si="4">+D15-D16</f>
+        <f t="shared" ref="D17:K17" si="8">+D15-D16</f>
         <v>360.35500000000002</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>385.822</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>421.87700000000007</v>
       </c>
       <c r="G17" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>489.39400000000006</v>
       </c>
       <c r="H17" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>461.572</v>
       </c>
       <c r="I17" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>516.00599999999997</v>
       </c>
       <c r="J17" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>573.36500000000001</v>
       </c>
       <c r="K17" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>626.82600000000002</v>
       </c>
       <c r="L17" s="3">
@@ -2282,27 +2340,27 @@
         <v>741.00900000000001</v>
       </c>
       <c r="O17" s="1">
-        <f t="shared" ref="O17:T17" si="5">+O15-O16</f>
+        <f t="shared" ref="O17:T17" si="9">+O15-O16</f>
         <v>746.80099999999993</v>
       </c>
       <c r="P17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>769.32199999999989</v>
       </c>
       <c r="Q17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>799.74599999999998</v>
       </c>
       <c r="R17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>865.57400000000007</v>
       </c>
       <c r="S17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>975.70299999999997</v>
       </c>
       <c r="T17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>914.08500000000015</v>
       </c>
       <c r="U17" s="1">
@@ -2321,6 +2379,10 @@
         <f>+X15-X16</f>
         <v>1149.9189999999999</v>
       </c>
+      <c r="Y17" s="1">
+        <f>+Y15-Y16</f>
+        <v>1174.6289999999999</v>
+      </c>
     </row>
     <row r="18" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
@@ -2391,6 +2453,9 @@
         <f>2669.312-SUM(U18:W18)</f>
         <v>700.67799999999988</v>
       </c>
+      <c r="Y18" s="1">
+        <v>755.99400000000003</v>
+      </c>
     </row>
     <row r="19" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -2463,6 +2528,9 @@
         <f>1134.535-SUM(U19:W19)</f>
         <v>314.41600000000005</v>
       </c>
+      <c r="Y19" s="1">
+        <v>336.42700000000002</v>
+      </c>
     </row>
     <row r="20" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
@@ -2533,6 +2601,9 @@
         <f>646.998-SUM(U20:W20)</f>
         <v>163.30400000000009</v>
       </c>
+      <c r="Y20" s="1">
+        <v>178.54499999999999</v>
+      </c>
     </row>
     <row r="21" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
@@ -2540,15 +2611,15 @@
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3">
-        <f t="shared" ref="D21:F21" si="6">SUM(D18:D20)</f>
+        <f t="shared" ref="D21:F21" si="10">SUM(D18:D20)</f>
         <v>363.64400000000001</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>373.89</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>394.16399999999999</v>
       </c>
       <c r="G21" s="3">
@@ -2572,56 +2643,60 @@
         <v>634.947</v>
       </c>
       <c r="L21" s="3">
-        <f t="shared" ref="L21:N21" si="7">SUM(L18:L20)</f>
+        <f t="shared" ref="L21:N21" si="11">SUM(L18:L20)</f>
         <v>671.77</v>
       </c>
       <c r="M21" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>702.02700000000004</v>
       </c>
       <c r="N21" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>815.99799999999993</v>
       </c>
       <c r="O21" s="1">
-        <f t="shared" ref="O21:X21" si="8">SUM(O18:O20)</f>
+        <f t="shared" ref="O21:Y21" si="12">SUM(O18:O20)</f>
         <v>908.36800000000017</v>
       </c>
       <c r="P21" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>819.71100000000001</v>
       </c>
       <c r="Q21" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>818.61500000000001</v>
       </c>
       <c r="R21" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>914.63599999999997</v>
       </c>
       <c r="S21" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>957.899</v>
       </c>
       <c r="T21" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>981.03500000000008</v>
       </c>
       <c r="U21" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1002.135</v>
       </c>
       <c r="V21" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1120.8150000000001</v>
       </c>
       <c r="W21" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1149.4970000000001</v>
       </c>
       <c r="X21" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1178.3980000000001</v>
+      </c>
+      <c r="Y21" s="1">
+        <f t="shared" si="12"/>
+        <v>1270.9660000000001</v>
       </c>
     </row>
     <row r="22" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -2630,15 +2705,15 @@
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3">
-        <f t="shared" ref="D22:F22" si="9">+D17-D21</f>
+        <f t="shared" ref="D22:F22" si="13">+D17-D21</f>
         <v>-3.2889999999999873</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>11.932000000000016</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>27.713000000000079</v>
       </c>
       <c r="G22" s="3">
@@ -2662,56 +2737,60 @@
         <v>-8.1209999999999809</v>
       </c>
       <c r="L22" s="3">
-        <f t="shared" ref="L22:N22" si="10">+L17-L21</f>
+        <f t="shared" ref="L22:N22" si="14">+L17-L21</f>
         <v>-42.33299999999997</v>
       </c>
       <c r="M22" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>-34.027000000000044</v>
       </c>
       <c r="N22" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>-74.988999999999919</v>
       </c>
       <c r="O22" s="1">
-        <f t="shared" ref="O22:X22" si="11">+O17-O21</f>
+        <f t="shared" ref="O22:Y22" si="15">+O17-O21</f>
         <v>-161.56700000000023</v>
       </c>
       <c r="P22" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-50.389000000000124</v>
       </c>
       <c r="Q22" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-18.869000000000028</v>
       </c>
       <c r="R22" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-49.061999999999898</v>
       </c>
       <c r="S22" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>17.803999999999974</v>
       </c>
       <c r="T22" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-66.949999999999932</v>
       </c>
       <c r="U22" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-31.977999999999838</v>
       </c>
       <c r="V22" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-57.479000000000042</v>
       </c>
       <c r="W22" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-12.456000000000131</v>
       </c>
       <c r="X22" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-28.479000000000269</v>
+      </c>
+      <c r="Y22" s="1">
+        <f t="shared" si="15"/>
+        <v>-96.337000000000216</v>
       </c>
       <c r="AA22" s="1" t="s">
         <v>7</v>
@@ -2719,8 +2798,8 @@
       <c r="AB22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AC22" s="16">
-        <v>0.18</v>
+      <c r="AC22" s="15">
+        <v>0.2</v>
       </c>
       <c r="AE22" s="1" t="s">
         <v>92</v>
@@ -2728,7 +2807,7 @@
       <c r="AF22" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AG22" s="16"/>
+      <c r="AG22" s="15"/>
     </row>
     <row r="23" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
@@ -2818,16 +2897,20 @@
         <f>112.324-30.55-50.277</f>
         <v>31.497</v>
       </c>
+      <c r="Y23" s="1">
+        <f>29.845+18.804-8.636</f>
+        <v>40.013000000000005</v>
+      </c>
       <c r="AB23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="16">
+      <c r="AC23" s="15">
         <v>0.01</v>
       </c>
       <c r="AF23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AG23" s="16">
+      <c r="AG23" s="15">
         <v>0.01</v>
       </c>
     </row>
@@ -2837,75 +2920,75 @@
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3">
-        <f t="shared" ref="D24:N24" si="12">+D22+D23</f>
+        <f t="shared" ref="D24:N24" si="16">+D22+D23</f>
         <v>-12.382999999999987</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>1.9470000000000169</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>29.825000000000081</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>68.220000000000041</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>-14.617000000000012</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>32.814999999999955</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>-72.718999999999966</v>
       </c>
       <c r="K24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>-13.536999999999981</v>
       </c>
       <c r="L24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>-46.379999999999967</v>
       </c>
       <c r="M24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>-5.7160000000000437</v>
       </c>
       <c r="N24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>-80.282999999999916</v>
       </c>
       <c r="O24" s="1">
-        <f t="shared" ref="O24:U24" si="13">+O22+O23</f>
+        <f t="shared" ref="O24:U24" si="17">+O22+O23</f>
         <v>-155.44100000000023</v>
       </c>
       <c r="P24" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-45.40600000000012</v>
       </c>
       <c r="Q24" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-10.954000000000031</v>
       </c>
       <c r="R24" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-40.108999999999895</v>
       </c>
       <c r="S24" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>19.774999999999977</v>
       </c>
       <c r="T24" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-54.118999999999929</v>
       </c>
       <c r="U24" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-30.163999999999838</v>
       </c>
       <c r="V24" s="1">
@@ -2920,16 +3003,20 @@
         <f>+X22+X23</f>
         <v>3.0179999999997307</v>
       </c>
+      <c r="Y24" s="1">
+        <f>+Y22+Y23</f>
+        <v>-56.324000000000211</v>
+      </c>
       <c r="AB24" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AC24" s="16">
+      <c r="AC24" s="15">
         <v>0.09</v>
       </c>
       <c r="AF24" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AG24" s="16">
+      <c r="AG24" s="15">
         <v>0.09</v>
       </c>
     </row>
@@ -3002,19 +3089,22 @@
         <f>-157.782+SUM(U25:W25)</f>
         <v>-136.60500000000002</v>
       </c>
+      <c r="Y25" s="1">
+        <v>-4.4539999999999997</v>
+      </c>
       <c r="AB25" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="AC25" s="17">
+      <c r="AC25" s="16">
         <f>NPV(AC24,AB11:CF11)</f>
-        <v>96980.510516830196</v>
+        <v>103589.61777221909</v>
       </c>
       <c r="AF25" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="AG25" s="18">
+      <c r="AG25" s="17">
         <f>NPV(AG24,AE14:CJ14)</f>
-        <v>33292.14877462099</v>
+        <v>35247.24074120685</v>
       </c>
     </row>
     <row r="26" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -3023,75 +3113,75 @@
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3">
-        <f t="shared" ref="D26:N26" si="14">+D24-D25</f>
+        <f t="shared" ref="D26:N26" si="18">+D24-D25</f>
         <v>-12.382999999999987</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>1.9470000000000169</v>
       </c>
       <c r="F26" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>29.825000000000081</v>
       </c>
       <c r="G26" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>68.220000000000041</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-14.617000000000012</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>32.814999999999955</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-72.718999999999966</v>
       </c>
       <c r="K26" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-13.536999999999981</v>
       </c>
       <c r="L26" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-90.638999999999967</v>
       </c>
       <c r="M26" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-13.741000000000044</v>
       </c>
       <c r="N26" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-80.282999999999916</v>
       </c>
       <c r="O26" s="1">
-        <f t="shared" ref="O26:U26" si="15">+O24-O25</f>
+        <f t="shared" ref="O26:U26" si="19">+O24-O25</f>
         <v>-209.03700000000023</v>
       </c>
       <c r="P26" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>-58.91200000000012</v>
       </c>
       <c r="Q26" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>-31.883000000000031</v>
       </c>
       <c r="R26" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>-84.468999999999895</v>
       </c>
       <c r="S26" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>12.751999999999978</v>
       </c>
       <c r="T26" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>-196.91899999999993</v>
       </c>
       <c r="U26" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>-123.76899999999983</v>
       </c>
       <c r="V26" s="1">
@@ -3106,6 +3196,10 @@
         <f>+X24-X25</f>
         <v>139.62299999999976</v>
       </c>
+      <c r="Y26" s="1">
+        <f>+Y24-Y25</f>
+        <v>-51.870000000000211</v>
+      </c>
       <c r="AB26" s="1" t="s">
         <v>1</v>
       </c>
@@ -3126,105 +3220,109 @@
         <v>24</v>
       </c>
       <c r="D27" s="10">
-        <f t="shared" ref="D27:N27" si="16">+D26/D28</f>
+        <f t="shared" ref="D27:N27" si="20">+D26/D28</f>
         <v>-5.0152080321089906E-2</v>
       </c>
       <c r="E27" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>7.8503316331674181E-3</v>
       </c>
       <c r="F27" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0.11968874905693726</v>
       </c>
       <c r="G27" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0.26739518986547944</v>
       </c>
       <c r="H27" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-5.81738728986246E-2</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0.13016350265364551</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-0.28747232764073355</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-5.3353460269664088E-2</v>
       </c>
       <c r="L27" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-0.35617057395022034</v>
       </c>
       <c r="M27" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-5.3851007379481064E-2</v>
       </c>
       <c r="N27" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-0.31375989744952559</v>
       </c>
       <c r="O27" s="13">
-        <f t="shared" ref="O27:X27" si="17">+O26/O28</f>
+        <f t="shared" ref="O27:Y27" si="21">+O26/O28</f>
         <v>-0.81392777182906739</v>
       </c>
       <c r="P27" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-0.22888313020369991</v>
       </c>
       <c r="Q27" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-0.12362208082758526</v>
       </c>
       <c r="R27" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-0.32663833473188386</v>
       </c>
       <c r="S27" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>4.8713031652774401E-2</v>
       </c>
       <c r="T27" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-0.75643231947634859</v>
       </c>
       <c r="U27" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-0.47516287426528964</v>
       </c>
       <c r="V27" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-0.14630840101552015</v>
       </c>
       <c r="W27" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.21357134971123523</v>
       </c>
       <c r="X27" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.53334581167131967</v>
+      </c>
+      <c r="Y27" s="13">
+        <f t="shared" si="21"/>
+        <v>-0.19723108395344408</v>
       </c>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AC27" s="17">
+      <c r="AC27" s="16">
         <f>AC25/AC26</f>
-        <v>370.45579236872038</v>
+        <v>395.7019171013805</v>
       </c>
       <c r="AD27" s="1"/>
       <c r="AE27" s="1"/>
       <c r="AF27" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AG27" s="17">
+      <c r="AG27" s="16">
         <f>AG25/AG26</f>
-        <v>127.1726585912249</v>
+        <v>134.64091318975676</v>
       </c>
     </row>
     <row r="28" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -3295,19 +3393,22 @@
       <c r="X28" s="1">
         <v>261.78699999999998</v>
       </c>
+      <c r="Y28" s="1">
+        <v>262.99099999999999</v>
+      </c>
       <c r="AB28" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="AC28" s="16">
+      <c r="AC28" s="20">
         <f>(AC27-Main!L2)/Main!L2</f>
-        <v>1.4776337103311956</v>
+        <v>1.3356269454691332</v>
       </c>
       <c r="AF28" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="AG28" s="16">
+      <c r="AG28" s="15">
         <f>(AG27-Main!L2)/Main!L2</f>
-        <v>-0.14946054981791804</v>
+        <v>-0.20528324170843601</v>
       </c>
     </row>
     <row r="30" spans="2:33" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3320,73 +3421,79 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="11">
-        <f t="shared" ref="H30:X30" si="18">+H15/D15-1</f>
+        <f t="shared" ref="H30:Y30" si="22">+H15/D15-1</f>
         <v>0.29981462381178048</v>
       </c>
       <c r="I30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.33626982019821283</v>
       </c>
       <c r="J30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.373319318093422</v>
       </c>
       <c r="K30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.30201256136501087</v>
       </c>
       <c r="L30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.35797683450125906</v>
       </c>
       <c r="M30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.31491928654254542</v>
       </c>
       <c r="N30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.26749607131756803</v>
       </c>
       <c r="O30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.23627836124949519</v>
       </c>
       <c r="P30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.235913829340612</v>
       </c>
       <c r="Q30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.21102884348618778</v>
       </c>
       <c r="R30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.21474176811381662</v>
       </c>
       <c r="S30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.29895035572552597</v>
       </c>
       <c r="T30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.20497541257674934</v>
       </c>
       <c r="U30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.21477947380532347</v>
       </c>
       <c r="V30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.21351840846704562</v>
       </c>
       <c r="W30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.1409335243977099</v>
       </c>
       <c r="X30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0.22336181832642543</v>
       </c>
+      <c r="Y30" s="11">
+        <f t="shared" si="22"/>
+        <v>0.20607502561499103</v>
+      </c>
+      <c r="AB30" s="23"/>
+      <c r="AC30" s="22"/>
     </row>
     <row r="31" spans="2:33" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
@@ -3413,178 +3520,196 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
+      <c r="AB31" s="21"/>
+      <c r="AC31" s="22"/>
     </row>
     <row r="32" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>13</v>
       </c>
       <c r="D32" s="6">
-        <f t="shared" ref="D32:K32" si="19">+D17/D15</f>
+        <f t="shared" ref="D32:K32" si="23">+D17/D15</f>
         <v>0.8371082243841701</v>
       </c>
       <c r="E32" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0.83964518417604983</v>
       </c>
       <c r="F32" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0.84146689298486721</v>
       </c>
       <c r="G32" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0.86050625254954916</v>
       </c>
       <c r="H32" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0.8249147959302211</v>
       </c>
       <c r="I32" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0.84036780321290372</v>
       </c>
       <c r="J32" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0.83274269962209113</v>
       </c>
       <c r="K32" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0.84650049764278035</v>
       </c>
       <c r="L32" s="6">
-        <f t="shared" ref="L32:W32" si="20">+L17/L15</f>
+        <f t="shared" ref="L32:Y32" si="24">+L17/L15</f>
         <v>0.82837988473904411</v>
       </c>
       <c r="M32" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.82735523760453422</v>
       </c>
       <c r="N32" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.84909545504546791</v>
       </c>
       <c r="O32" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.81577208223688158</v>
       </c>
       <c r="P32" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.81921375617880132</v>
       </c>
       <c r="Q32" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.81792436910332134</v>
       </c>
       <c r="R32" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.81649451472017054</v>
       </c>
       <c r="S32" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.82051974219764401</v>
       </c>
       <c r="T32" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.80778815648777391</v>
       </c>
       <c r="U32" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.81678103960241832</v>
       </c>
       <c r="V32" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.82655777896449412</v>
       </c>
       <c r="W32" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0.8380832834579971</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="X32" s="6">
+        <f t="shared" si="24"/>
+        <v>0.83065986488907373</v>
+      </c>
+      <c r="Y32" s="6">
+        <f t="shared" si="24"/>
+        <v>0.81995500340999605</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="6">
-        <f t="shared" ref="D33:K33" si="21">+D22/D15</f>
+        <f t="shared" ref="D33:K33" si="25">+D22/D15</f>
         <v>-7.640379486893549E-3</v>
       </c>
       <c r="E33" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>2.5967016752773665E-2</v>
       </c>
       <c r="F33" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>5.5275760483007343E-2</v>
       </c>
       <c r="G33" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0.13599998593352186</v>
       </c>
       <c r="H33" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>-1.3450358241337978E-2</v>
       </c>
       <c r="I33" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>6.4567508761872436E-2</v>
       </c>
       <c r="J33" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>-9.6899753967170377E-2</v>
       </c>
       <c r="K33" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>-1.0967047540078111E-2</v>
       </c>
       <c r="L33" s="6">
-        <f t="shared" ref="L33:W33" si="22">+L22/L15</f>
+        <f t="shared" ref="L33:Y33" si="26">+L22/L15</f>
         <v>-5.5712971529569964E-2</v>
       </c>
       <c r="M33" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>-4.21443363322897E-2</v>
       </c>
       <c r="N33" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>-8.5927187224992582E-2</v>
       </c>
       <c r="O33" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>-0.17648857997079068</v>
       </c>
       <c r="P33" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>-5.3656806850829332E-2</v>
       </c>
       <c r="Q33" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>-1.929789573265836E-2</v>
       </c>
       <c r="R33" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>-4.6280103008178294E-2</v>
       </c>
       <c r="S33" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>1.4972315848251807E-2</v>
       </c>
       <c r="T33" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>-5.9164538392880744E-2</v>
       </c>
       <c r="U33" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>-2.6922471398346862E-2</v>
       </c>
       <c r="V33" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>-4.4679870311077771E-2</v>
       </c>
       <c r="W33" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>-9.1809929270386219E-3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="X33" s="6">
+        <f t="shared" si="26"/>
+        <v>-2.0572198817635116E-2</v>
+      </c>
+      <c r="Y33" s="6">
+        <f t="shared" si="26"/>
+        <v>-6.7248471784290165E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -3606,10 +3731,13 @@
       <c r="V34" s="6"/>
       <c r="W34" s="6"/>
     </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>92</v>
       </c>
+      <c r="T35">
+        <v>413.61399999999998</v>
+      </c>
       <c r="U35">
         <v>74.340999999999994</v>
       </c>
@@ -3622,14 +3750,17 @@
       <c r="X35">
         <v>360.31799999999998</v>
       </c>
-    </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="U36" s="16"/>
-      <c r="V36" s="16"/>
-      <c r="W36" s="16"/>
-      <c r="X36" s="16"/>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35">
+        <v>114.60299999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="U36" s="15"/>
+      <c r="V36" s="15"/>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>3</v>
       </c>
@@ -3638,7 +3769,7 @@
         <v>2562.1239999999998</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>54</v>
       </c>
@@ -3646,7 +3777,7 @@
         <v>628.04899999999998</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
         <v>55</v>
       </c>
@@ -3654,7 +3785,7 @@
         <v>109.312</v>
       </c>
     </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
         <v>56</v>
       </c>
@@ -3662,7 +3793,7 @@
         <v>86.314999999999998</v>
       </c>
     </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
         <v>57</v>
       </c>
@@ -3670,7 +3801,7 @@
         <v>172.46799999999999</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
         <v>58</v>
       </c>
@@ -3679,7 +3810,7 @@
         <v>1587.8130000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
         <v>59</v>
       </c>
@@ -3687,7 +3818,7 @@
         <v>3.9340000000000002</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
         <v>60</v>
       </c>
@@ -3695,7 +3826,7 @@
         <v>62.118000000000002</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
         <v>61</v>
       </c>
@@ -3704,10 +3835,10 @@
         <v>5212.1330000000007</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="T46" s="1"/>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
         <v>62</v>
       </c>
@@ -3715,7 +3846,7 @@
         <v>177.54499999999999</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
         <v>63</v>
       </c>
